--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanch\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A72FD3-C774-403C-95B8-5FFAFB6C160D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D96B4E-3586-406C-AD99-2C0AF8E5232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$21</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Domain</t>
   </si>
@@ -44,285 +44,6 @@
   </si>
   <si>
     <t>Pick Count</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Core Concept of Business &amp; Assets</t>
-  </si>
-  <si>
-    <t>Introduction to Business</t>
-  </si>
-  <si>
-    <t>Assets: Resources that help us earn money</t>
-  </si>
-  <si>
-    <t>A business fundamentally exists to earn money. To achieve this, it must offer a product, service, or value proposition that others are willing to purchase.
-To produce or create this offering, certain resources are required. The resources that help a business generate income and earn money are called assets. Therefore, assets are the engine of a business's revenue generation.</t>
-  </si>
-  <si>
-    <t>Funding Sources: Equity vs. Liabilities</t>
-  </si>
-  <si>
-    <t>Capital Structure</t>
-  </si>
-  <si>
-    <t>Assets = Funding (Equity + Liabilities)</t>
-  </si>
-  <si>
-    <t>To acquire assets, a business needs capital or funding. This money can come from two distinct sources: the owners themselves (equity) or external parties (liabilities/borrowings).
-If we borrow money from someone and have an obligation to repay it in the future, it is called a liability. If, instead of requiring repayment, the person provides money in exchange for a share in the profits, it is called equity. Equity represents the 'distribution of something as per contribution' and determines how much control a shareholder has. In a company, all assets must equal total funding (Assets = Equity + Liabilities) because any funding raised is used to acquire the assets of the firm.</t>
-  </si>
-  <si>
-    <t>Assets vs. Expenses</t>
-  </si>
-  <si>
-    <t>Financial Concepts</t>
-  </si>
-  <si>
-    <t>Assets (Create money) vs. Expenses (Consume money)</t>
-  </si>
-  <si>
-    <t>It is critical for a business to distinguish between money spent to build future earning power and money that is consumed in current operations.
-An asset is a resource used to generate money over time. An expense, on the other hand, is a cash outflow for items or services that are consumed immediately and do not generate future revenue. While assets build the business's capacity to earn, expenses represent the cost of running the business today.</t>
-  </si>
-  <si>
-    <t>Revenue and Cost of Goods Sold (COGS)</t>
-  </si>
-  <si>
-    <t>Profitability</t>
-  </si>
-  <si>
-    <t>Revenue/Profit = Unit Value (Selling Price) - COGS (Cost Price)</t>
-  </si>
-  <si>
-    <t>To make money, a business must sell its offerings at a price that exceeds the cost incurred to produce them. The cost of manufacturing or procuring these items is known as the Cost of Goods Sold (COGS).
-The revenue or profit generated from each sale is determined by subtracting the COGS (cost price) from the unit value (selling price). Maximizing profitability requires either increasing the unit selling price or lowering the cost of goods sold without sacrificing quality.</t>
-  </si>
-  <si>
-    <t>Revenue vs. Cash Flow</t>
-  </si>
-  <si>
-    <t>Working Capital</t>
-  </si>
-  <si>
-    <t>Revenue (Accrued Sale) != Cash (Physical Money)</t>
-  </si>
-  <si>
-    <t>In business, making a sale does not always mean receiving immediate cash. While businesses prefer prompt cash payments, many offer goods or services on credit (sell first, collect later) to boost sales volume. A transaction is counted as a successful sale and recorded as revenue as soon as the credit sale occurs.
-This creates a key distinction between revenue and cash. You can increase revenue by making a sale on credit today; however, the actual cash on hand will not increase until the customer pays the invoice. This delay is why a highly profitable business on paper can still face cash shortages if it manages its receivables poorly.</t>
-  </si>
-  <si>
-    <t>Financial Statements: Stock vs. Flow</t>
-  </si>
-  <si>
-    <t>Financial Reporting</t>
-  </si>
-  <si>
-    <t>Balance Sheet (Stock) | P&amp;L &amp; Cash Flow (Flow)</t>
-  </si>
-  <si>
-    <t>Businesses track their financial activities using three primary statements, which are classified as either 'Stock' or 'Flow' concepts depending on whether they measure data at a single point in time or over an interval.
-A stock concept measures financial position at a single, specific point in time. The Balance Sheet is a stock concept, tracking assets and funding at a precise moment. A flow concept measures financial activity over a period or time interval. The Profit &amp; Loss Statement (which tracks performance/profitability) and the Cash Flow Statement (which tracks cash movements) are both flow concepts.</t>
-  </si>
-  <si>
-    <t>Asset Risks &amp; Dual Purpose</t>
-  </si>
-  <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>Dual Purpose: Income Generation &amp; Risk Management</t>
-  </si>
-  <si>
-    <t>While assets are designed to earn money, they also carry inherent trade-offs in the form of risks. These risks include physical damage (e.g., equipment breaking down) or the uncertainty of future benefits (such as purchasing a fleet of cars for a taxi business just before a global pandemic restricts travel).
-To balance these risks, assets serve a dual purpose. They are categorized either as income generation assets (which actively help create revenue) or risk management assets (which reduce the risk or volatility of creating that revenue).</t>
-  </si>
-  <si>
-    <t>Income Generating Assets (Non-Current Assets)</t>
-  </si>
-  <si>
-    <t>Non-Current Assets (Long-term, &gt;12 Months)</t>
-  </si>
-  <si>
-    <t>Income generating assets, often referred to as capital assets, are long-term resources used to produce goods and services. They provide economic benefits over multiple years and are reported on the Balance Sheet as Non-Current Assets.
-These assets can be tangible or intangible. Tangible assets have a physical form, such as factories, machinery, equipment, and company vehicles. Intangible assets do not have a physical presence but hold immense economic value, such as patents, brand names, copyrights, and goodwill.</t>
-  </si>
-  <si>
-    <t>Risk Management Assets (Current Assets)</t>
-  </si>
-  <si>
-    <t>Current Assets (Short-term, &lt;=12 Months)</t>
-  </si>
-  <si>
-    <t>Risk management assets are short-term resources held by a company to ensure smooth business operations and mitigate liquidity risks. These assets are expected to be consumed, sold, or converted into cash within a 12-month period.
-On the Balance Sheet, they are classified as Current Assets. Typical examples include inventories (goods ready for sale), receivables (money owed by credit customers), short-term investments, and cash on hand. Having adequate current assets protects the business against sudden cash shortages.</t>
-  </si>
-  <si>
-    <t>Goodwill</t>
-  </si>
-  <si>
-    <t>Mergers &amp; Acquisitions</t>
-  </si>
-  <si>
-    <t>Goodwill = Fair Value (Purchase Price) - Book Value</t>
-  </si>
-  <si>
-    <t>Goodwill is an intangible asset that is created when one company acquires another. It represents the premium paid by the acquirer over the fair market value of the target company's identifiable net physical assets.
-This extra price is paid because the target company possesses highly valuable, non-physical assets that are not fully captured on its balance sheet. These include loyal customer relationships, strong brand recognition, proprietary technologies, or employee expertise. Goodwill is reported as a non-current asset on the acquirer's balance sheet post-acquisition.</t>
-  </si>
-  <si>
-    <t>Goodwill Impairment</t>
-  </si>
-  <si>
-    <t>Impairment = Asset Write-down</t>
-  </si>
-  <si>
-    <t>While goodwill is recorded during an acquisition, there is no guarantee that its value will remain intact forever. When the acquired brand, customer loyalty, or business synergies lose their economic value over time, the goodwill is considered 'impaired.'
-When a goodwill impairment occurs, the business must write down the asset's value. This write-down causes two simultaneous adjustments: (1) On the Income Statement (Profit &amp; Loss), a 'goodwill impairment loss' is reported as an operating expense, reducing net income. (2) On the Balance Sheet, the value of intangible assets decreases, and the company's Retained Earnings (under the equity section) drop by the exact same amount.</t>
-  </si>
-  <si>
-    <t>Retained Earnings</t>
-  </si>
-  <si>
-    <t>Retained Earnings = Cumulative Profits - Dividends</t>
-  </si>
-  <si>
-    <t>Retained earnings represent the accumulated profits of a business that have not been distributed to shareholders as dividends. Instead, this capital is kept by the firm to be reinvested into its core operations.
-Retained earnings are reported under the equity section of the Balance Sheet. They are used for purchasing new assets, funding research and development, paying down debt, or general business expansion. Over time, healthy retained earnings signify a self-sustaining and growing business.</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Anchoring effect</t>
-  </si>
-  <si>
-    <t>Consumer psychology</t>
-  </si>
-  <si>
-    <t>₹1,500 feels cheap when we see “₹3,000 → ₹1,500,” even though ₹1,500 might not feel cheap if shown by itself.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discounts exploit several psychological biases. A discounted product can feel like a bargain because we compare its sale price with the artificially prominent original price. This is called the **anchoring effect**. For example, ₹1,500 feels cheap when we see “₹3,000 → ₹1,500,” even though ₹1,500 might not feel cheap if shown by itself.
-Discounts also create **urgency and fear of missing out**. Phrases like “50% off,” “today only,” or “last 3 left” shift our thinking from “Do I need this?” to “Can I afford to miss this opportunity?” This can make us buy things we otherwise wouldn't.
-The biggest mistake is treating money not spent as money “saved.” If you buy an unnecessary ₹1,500 item because it was 50% off, you haven't saved ₹1,500. You have **spent ₹1,500**. A discount is genuine savings only when you already intended to buy the item and get it for less than you expected to pay.
-A useful rule is therefore: **Don't ask, “How much am I saving?” Ask, “Would I buy this if there were no discount?”** If the answer is no, the discount may be creating the desire rather than satisfying an existing need.
-</t>
-  </si>
-  <si>
-    <t>UTM (Urchin Tracking Module)</t>
-  </si>
-  <si>
-    <t>Digital marketing</t>
-  </si>
-  <si>
-    <t>Snippet of text added to a web link that tracks website traffic, letting marketers see exactly which specific post, ad, or platform drove a visitor to their site. Like `&amp;utm_medium=web3x&amp;utm_name=web3xcss&amp;utm_source=share&amp;utm_term=1`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An Urchin Tracking Module (UTM) is basically a simple code that you attach to the end of a website link to track how people found it. If you have ever clicked a link on social media and noticed a massive string of random words, question marks, and equal signs in your browser’s address bar, you have seen a UTM code in action. It doesn't change where the link takes you; it just acts like a digital tracker. 
-When someone clicks that link, tools like Google Analytics read those extra words and log exactly where that visitor came from. For businesses and content creators, these codes are pure gold because they take the guessing out of marketing. 
-Imagine you are promoting a new sneaker launch and you post the link on TikTok, Instagram, and in an email newsletter. By giving each platform its own unique UTM link, you can see exactly which app is driving the most sales. If 90% of your buyers come from the TikTok link and only 2% from email, you instantly know where to spend your energy. It helps creators and companies figure out if their ads are actually working or if they are just wasting money.
-To make this happen, a UTM code uses five main labels, though you usually only need three. First is the source, which names the specific platform, like "instagram" or "google." Next is the medium, which explains the broader channel type, like "organic_social" for free posts or "cpc" for paid ads. Then there is the campaign, which is just the name of your project, like "summer_sale_2026." There are also labels for term (to track specific search keywords) and content (to tell apart two different buttons in the exact same email). Put them all together, and a normal link turns into a smart link that tells you a story about your audience.
-</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>Inventory management</t>
-  </si>
-  <si>
-    <t>Waste tracking and optimzation for restaurants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**TL;DR:** measuring and reducing wastage**. If the increase is instead driven by higher market prices, the restaurant can respond through **ingredient substitution, selective price or portion changes, and recipe/product optimization**. The key objective is simple: **generate the same revenue while using fewer resources or getting more revenue from every rupee spent on raw materials.**
-</t>
-  </si>
-  <si>
-    <t>Imagine a restaurant whose revenue this year is almost the same as last year, but its profitability has fallen. Since Revenue = Quantity Sold × Average Selling Price, if neither quantity sold nor average selling price has changed meaningfully, the next question is whether the restaurant has become less efficient at converting raw materials into food that is actually sold. Raw-material consumption can broadly be divided into Recipe/Portion Usage + Wastage + Other Uses. Wastage itself can come from expiry, preparation errors, and overproduction. Overproduction is particularly relevant in restaurants because food is often prepared before customers arrive. For example, if 100 portions are prepared but only 80 are sold, the remaining 20 portions represent potential waste. Therefore, the objective of inventory management is not simply to buy cheaper ingredients, but to buy, store and use the right quantity of ingredients with minimum waste.
-This can be achieved through three levers. First, better demand forecasting helps the restaurant estimate customer demand and prepare or stock only what is required, with a reasonable safety margin. Second, stricter inventory controls reduce spoilage. Techniques such as FIFO (First In, First Out) ensure older inventory is used first, while FEFO (First Expiry, First Out) prioritizes ingredients that will expire sooner. Third, wastage measurement helps identify where and why waste occurs. For example, tracking waste by outlet, ingredient, dish or reason can reveal that one restaurant store consistently wastes more vegetables than others, pointing to problems in forecasting, preparation or storage.
-However, raw-material costs can increase even when the restaurant's own processes are efficient. Raw materials can broadly come from sources such as agriculture, dairy, poultry and mining, and the final purchase price can be viewed as Market Price + Supplier Premium/Discount. Market prices are influenced by factors such as global demand and supply, farmer input costs, exchange rates and inflation. The supplier premium or discount, meanwhile, depends on factors such as purchase volume and bargaining power. Larger volumes can create economies of scale, while bargaining power increases when the restaurant has multiple alternative suppliers and switching between them is relatively easy. This distinction is important because it separates factors the restaurant can control from those it cannot.
-If the market price of an ingredient rises, the restaurant has three broad strategic responses. It can substitute ingredients where a lower-cost alternative can provide a similar customer experience. It can use selective price increases or portion changes for dishes that are particularly affected by input-cost inflation, rather than increasing prices across the entire menu. Finally, it can pursue recipe and product optimization, reducing the quantity or cost of ingredients without materially affecting the customer's perception of value.
-Ultimately, inventory management is about one question: How can a restaurant generate the same revenue while extracting more value from every rupee spent on raw materials? This makes inventory management more than a back-end operational activity. It is a direct link between customer demand, procurement, kitchen operations, and profitability.</t>
-  </si>
-  <si>
-    <t>Product management</t>
-  </si>
-  <si>
-    <t>Automation Matrix</t>
-  </si>
-  <si>
-    <t>Automation</t>
-  </si>
-  <si>
-    <t>While deciding what we should automate or not, we can follow a 2x2 matrix as a guideline</t>
-  </si>
-  <si>
-    <t>A combination of repeatbility and sensitivity defines whether we should automate something or not
-- Repeatability : How repetitive something is
-- Sensitivity : How much human involement is necessary
-Based on their intensity
-- High Repeatibility, Low Sensitivty = Fully automate
-- High Repeatibility, High Sensitivty = Automate + human in the loop
-- Low Repeatibility, High Sensitivty = Human led only
-- Low Repeatibility, Low Sensitivty = Ignore</t>
-  </si>
-  <si>
-    <t>Price level changes</t>
-  </si>
-  <si>
-    <t>Money</t>
-  </si>
-  <si>
-    <t>Overall rise (inflation) or fall (deflation) in the average cost of goods and services across an entire economy over time</t>
-  </si>
-  <si>
-    <t>Accounting (balance sheet and such) records only book value (the price at that time) and does not consider price-level changes</t>
-  </si>
-  <si>
-    <t>Steps of accounting</t>
-  </si>
-  <si>
-    <t>Accounting</t>
-  </si>
-  <si>
-    <t>Accounting is the language that enables communication of financial activities of a business. There are some steps of processing financial information</t>
-  </si>
-  <si>
-    <t>Steps are
-        - Identify transactions and events to be recorded
-        - Measure the transactions : Monetary units
-        - Record them : Journal
-        - Classify them : Ledger
-        - Summarise them : Trial balance, P&amp;L statement, Balance sheet
-        - Analysis and interpretation : Cash flow statement and Ratio analysis
-        - Communicating : Report creation</t>
-  </si>
-  <si>
-    <t>Debentures</t>
-  </si>
-  <si>
-    <t>Debt Instruments</t>
-  </si>
-  <si>
-    <t>A formal **"I.O.U." note** issued by a private / public companies. Instead of bank giving them a loan, normal people can buy debentures for money</t>
-  </si>
-  <si>
-    <t>- Customer buy debentures for a term (5 years). Suppose a debenture of 10k
-- Company promised to pay amount (10k) in 5 years and every year, pays interest
-- Note that secured debentures are better than unsecured because they protect customers if a company goes bankrupt</t>
-  </si>
-  <si>
-    <t>Bonds</t>
-  </si>
-  <si>
-    <t>A big ass debenture, usually by mega-corporations and govts. Extremely safe unlike debentures. Lower interest rates</t>
-  </si>
-  <si>
-    <t>A debenture is a formal **"I.O.U." note** issued by a private / public companies. Instead of bank giving them a loan, normal people can buy debentures for money. 
-Bonds are just extremely big debentures</t>
   </si>
 </sst>
 </file>
@@ -382,22 +103,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF535FC1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF535FC1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF535FC1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF535FC1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -502,25 +207,41 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF535FC1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF535FC1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF535FC1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF535FC1"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="Knowledge-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
     <tableStyle name="Compounding Reminder-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="Master Quotes-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -535,7 +256,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic"/>
@@ -801,24 +522,12 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4">
-        <v>3</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -842,24 +551,12 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -883,24 +580,12 @@
       <c r="AA3" s="1"/>
     </row>
     <row r="4" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="4">
-        <v>3</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -924,24 +609,12 @@
       <c r="AA4" s="1"/>
     </row>
     <row r="5" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="4">
-        <v>3</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -965,24 +638,12 @@
       <c r="AA5" s="1"/>
     </row>
     <row r="6" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="4">
-        <v>3</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1006,24 +667,12 @@
       <c r="AA6" s="1"/>
     </row>
     <row r="7" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="4">
-        <v>3</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1047,24 +696,12 @@
       <c r="AA7" s="1"/>
     </row>
     <row r="8" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="4">
-        <v>2</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -1088,24 +725,12 @@
       <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="4">
-        <v>2</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1129,24 +754,12 @@
       <c r="AA9" s="1"/>
     </row>
     <row r="10" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="4">
-        <v>3</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1170,24 +783,12 @@
       <c r="AA10" s="1"/>
     </row>
     <row r="11" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="4">
-        <v>3</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1211,24 +812,12 @@
       <c r="AA11" s="1"/>
     </row>
     <row r="12" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="4">
-        <v>3</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1252,24 +841,12 @@
       <c r="AA12" s="1"/>
     </row>
     <row r="13" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4">
-        <v>3</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1293,24 +870,12 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="4">
-        <v>2</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1334,24 +899,12 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="4">
-        <v>3</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1375,24 +928,12 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="4">
-        <v>2</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1416,24 +957,12 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="4">
-        <v>2</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1457,24 +986,12 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="4">
-        <v>3</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1498,24 +1015,12 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="4">
-        <v>2</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1539,24 +1044,12 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="4">
-        <v>3</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1580,24 +1073,12 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" s="4">
-        <v>3</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -29403,12 +28884,6 @@
       <c r="AA979" s="1"/>
     </row>
     <row r="980" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A980" s="1"/>
-      <c r="B980" s="1"/>
-      <c r="C980" s="1"/>
-      <c r="D980" s="1"/>
-      <c r="E980" s="1"/>
-      <c r="F980" s="1"/>
       <c r="G980" s="1"/>
       <c r="H980" s="1"/>
       <c r="I980" s="1"/>
@@ -29432,12 +28907,6 @@
       <c r="AA980" s="1"/>
     </row>
     <row r="981" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A981" s="1"/>
-      <c r="B981" s="1"/>
-      <c r="C981" s="1"/>
-      <c r="D981" s="1"/>
-      <c r="E981" s="1"/>
-      <c r="F981" s="1"/>
       <c r="G981" s="1"/>
       <c r="H981" s="1"/>
       <c r="I981" s="1"/>
@@ -29461,12 +28930,6 @@
       <c r="AA981" s="1"/>
     </row>
     <row r="982" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A982" s="1"/>
-      <c r="B982" s="1"/>
-      <c r="C982" s="1"/>
-      <c r="D982" s="1"/>
-      <c r="E982" s="1"/>
-      <c r="F982" s="1"/>
       <c r="G982" s="1"/>
       <c r="H982" s="1"/>
       <c r="I982" s="1"/>
@@ -29490,12 +28953,6 @@
       <c r="AA982" s="1"/>
     </row>
     <row r="983" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A983" s="1"/>
-      <c r="B983" s="1"/>
-      <c r="C983" s="1"/>
-      <c r="D983" s="1"/>
-      <c r="E983" s="1"/>
-      <c r="F983" s="1"/>
       <c r="G983" s="1"/>
       <c r="H983" s="1"/>
       <c r="I983" s="1"/>
@@ -29519,12 +28976,6 @@
       <c r="AA983" s="1"/>
     </row>
     <row r="984" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A984" s="1"/>
-      <c r="B984" s="1"/>
-      <c r="C984" s="1"/>
-      <c r="D984" s="1"/>
-      <c r="E984" s="1"/>
-      <c r="F984" s="1"/>
       <c r="G984" s="1"/>
       <c r="H984" s="1"/>
       <c r="I984" s="1"/>
@@ -29548,12 +28999,6 @@
       <c r="AA984" s="1"/>
     </row>
     <row r="985" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A985" s="1"/>
-      <c r="B985" s="1"/>
-      <c r="C985" s="1"/>
-      <c r="D985" s="1"/>
-      <c r="E985" s="1"/>
-      <c r="F985" s="1"/>
       <c r="G985" s="1"/>
       <c r="H985" s="1"/>
       <c r="I985" s="1"/>
@@ -29577,12 +29022,6 @@
       <c r="AA985" s="1"/>
     </row>
     <row r="986" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A986" s="1"/>
-      <c r="B986" s="1"/>
-      <c r="C986" s="1"/>
-      <c r="D986" s="1"/>
-      <c r="E986" s="1"/>
-      <c r="F986" s="1"/>
       <c r="G986" s="1"/>
       <c r="H986" s="1"/>
       <c r="I986" s="1"/>
@@ -29606,12 +29045,6 @@
       <c r="AA986" s="1"/>
     </row>
     <row r="987" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A987" s="1"/>
-      <c r="B987" s="1"/>
-      <c r="C987" s="1"/>
-      <c r="D987" s="1"/>
-      <c r="E987" s="1"/>
-      <c r="F987" s="1"/>
       <c r="G987" s="1"/>
       <c r="H987" s="1"/>
       <c r="I987" s="1"/>
@@ -29635,12 +29068,6 @@
       <c r="AA987" s="1"/>
     </row>
     <row r="988" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A988" s="1"/>
-      <c r="B988" s="1"/>
-      <c r="C988" s="1"/>
-      <c r="D988" s="1"/>
-      <c r="E988" s="1"/>
-      <c r="F988" s="1"/>
       <c r="G988" s="1"/>
       <c r="H988" s="1"/>
       <c r="I988" s="1"/>
@@ -29664,12 +29091,6 @@
       <c r="AA988" s="1"/>
     </row>
     <row r="989" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A989" s="1"/>
-      <c r="B989" s="1"/>
-      <c r="C989" s="1"/>
-      <c r="D989" s="1"/>
-      <c r="E989" s="1"/>
-      <c r="F989" s="1"/>
       <c r="G989" s="1"/>
       <c r="H989" s="1"/>
       <c r="I989" s="1"/>
@@ -29693,12 +29114,6 @@
       <c r="AA989" s="1"/>
     </row>
     <row r="990" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A990" s="1"/>
-      <c r="B990" s="1"/>
-      <c r="C990" s="1"/>
-      <c r="D990" s="1"/>
-      <c r="E990" s="1"/>
-      <c r="F990" s="1"/>
       <c r="G990" s="1"/>
       <c r="H990" s="1"/>
       <c r="I990" s="1"/>
@@ -29722,12 +29137,6 @@
       <c r="AA990" s="1"/>
     </row>
     <row r="991" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A991" s="1"/>
-      <c r="B991" s="1"/>
-      <c r="C991" s="1"/>
-      <c r="D991" s="1"/>
-      <c r="E991" s="1"/>
-      <c r="F991" s="1"/>
       <c r="G991" s="1"/>
       <c r="H991" s="1"/>
       <c r="I991" s="1"/>
@@ -29751,12 +29160,6 @@
       <c r="AA991" s="1"/>
     </row>
     <row r="992" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A992" s="1"/>
-      <c r="B992" s="1"/>
-      <c r="C992" s="1"/>
-      <c r="D992" s="1"/>
-      <c r="E992" s="1"/>
-      <c r="F992" s="1"/>
       <c r="G992" s="1"/>
       <c r="H992" s="1"/>
       <c r="I992" s="1"/>
@@ -29779,13 +29182,7 @@
       <c r="Z992" s="1"/>
       <c r="AA992" s="1"/>
     </row>
-    <row r="993" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A993" s="1"/>
-      <c r="B993" s="1"/>
-      <c r="C993" s="1"/>
-      <c r="D993" s="1"/>
-      <c r="E993" s="1"/>
-      <c r="F993" s="1"/>
+    <row r="993" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G993" s="1"/>
       <c r="H993" s="1"/>
       <c r="I993" s="1"/>
@@ -29808,13 +29205,7 @@
       <c r="Z993" s="1"/>
       <c r="AA993" s="1"/>
     </row>
-    <row r="994" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A994" s="1"/>
-      <c r="B994" s="1"/>
-      <c r="C994" s="1"/>
-      <c r="D994" s="1"/>
-      <c r="E994" s="1"/>
-      <c r="F994" s="1"/>
+    <row r="994" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G994" s="1"/>
       <c r="H994" s="1"/>
       <c r="I994" s="1"/>
@@ -29837,13 +29228,7 @@
       <c r="Z994" s="1"/>
       <c r="AA994" s="1"/>
     </row>
-    <row r="995" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A995" s="1"/>
-      <c r="B995" s="1"/>
-      <c r="C995" s="1"/>
-      <c r="D995" s="1"/>
-      <c r="E995" s="1"/>
-      <c r="F995" s="1"/>
+    <row r="995" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G995" s="1"/>
       <c r="H995" s="1"/>
       <c r="I995" s="1"/>
@@ -29866,13 +29251,7 @@
       <c r="Z995" s="1"/>
       <c r="AA995" s="1"/>
     </row>
-    <row r="996" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A996" s="1"/>
-      <c r="B996" s="1"/>
-      <c r="C996" s="1"/>
-      <c r="D996" s="1"/>
-      <c r="E996" s="1"/>
-      <c r="F996" s="1"/>
+    <row r="996" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G996" s="1"/>
       <c r="H996" s="1"/>
       <c r="I996" s="1"/>
@@ -29895,13 +29274,7 @@
       <c r="Z996" s="1"/>
       <c r="AA996" s="1"/>
     </row>
-    <row r="997" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A997" s="1"/>
-      <c r="B997" s="1"/>
-      <c r="C997" s="1"/>
-      <c r="D997" s="1"/>
-      <c r="E997" s="1"/>
-      <c r="F997" s="1"/>
+    <row r="997" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G997" s="1"/>
       <c r="H997" s="1"/>
       <c r="I997" s="1"/>
@@ -29924,13 +29297,7 @@
       <c r="Z997" s="1"/>
       <c r="AA997" s="1"/>
     </row>
-    <row r="998" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A998" s="1"/>
-      <c r="B998" s="1"/>
-      <c r="C998" s="1"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-      <c r="F998" s="1"/>
+    <row r="998" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G998" s="1"/>
       <c r="H998" s="1"/>
       <c r="I998" s="1"/>
@@ -29953,7 +29320,7 @@
       <c r="Z998" s="1"/>
       <c r="AA998" s="1"/>
     </row>
-    <row r="999" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="999" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G999" s="1"/>
       <c r="H999" s="1"/>
       <c r="I999" s="1"/>
@@ -29976,7 +29343,7 @@
       <c r="Z999" s="1"/>
       <c r="AA999" s="1"/>
     </row>
-    <row r="1000" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="1000" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G1000" s="1"/>
       <c r="H1000" s="1"/>
       <c r="I1000" s="1"/>
@@ -30003,7 +29370,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{E43654A1-81D9-4B52-93E5-7C243FB047DA}"/>
+      <autoFilter ref="A1:F23" xr:uid="{ADE12AA3-828E-4F07-8DDE-5F2D7ABC0106}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D96B4E-3586-406C-AD99-2C0AF8E5232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB38290-AE72-4E63-B65C-9C8256813EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Domain</t>
   </si>
@@ -44,6 +44,31 @@
   </si>
   <si>
     <t>Pick Count</t>
+  </si>
+  <si>
+    <t>Consulting</t>
+  </si>
+  <si>
+    <t>Guesstimates</t>
+  </si>
+  <si>
+    <t>When we are creating the issue tree using demand-side methodology, we can use some standard parameters</t>
+  </si>
+  <si>
+    <t>The parameters in question are
+- Age
+- Income
+- Location
+- Gender
+- Occupation
+- Country
+- Literacy rate
+- Mobile peneteration
+- Internet peneteration
+These allow us to segment the population correctly</t>
+  </si>
+  <si>
+    <t>Demand Side Parameter selection</t>
   </si>
 </sst>
 </file>
@@ -102,7 +127,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -226,22 +269,22 @@
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="Knowledge-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="firstRowStripe" dxfId="9"/>
-      <tableStyleElement type="secondRowStripe" dxfId="8"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
     <tableStyle name="Compounding Reminder-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" dxfId="5"/>
-      <tableStyleElement type="secondRowStripe" dxfId="4"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" dxfId="5"/>
     </tableStyle>
     <tableStyle name="Master Quotes-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -259,7 +302,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Category"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Definition/Formula"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Explanation"/>
@@ -477,7 +520,7 @@
     <col min="2" max="2" width="15.59765625" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="27.46484375" customWidth="1"/>
-    <col min="5" max="5" width="124.46484375" customWidth="1"/>
+    <col min="5" max="5" width="59.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -521,13 +564,25 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+    <row r="2" spans="1:27" ht="153" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -29370,7 +29425,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{ADE12AA3-828E-4F07-8DDE-5F2D7ABC0106}"/>
+      <autoFilter ref="A1:F23" xr:uid="{23B6EFED-7FB9-447D-B22A-CEE89816EAB1}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB38290-AE72-4E63-B65C-9C8256813EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42DDC7D-5994-46B3-AFFC-D4694E6FBEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="450" windowWidth="19320" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
@@ -46,29 +46,54 @@
     <t>Pick Count</t>
   </si>
   <si>
-    <t>Consulting</t>
+    <t>Finance</t>
   </si>
   <si>
-    <t>Guesstimates</t>
+    <t>Journal Entries</t>
   </si>
   <si>
-    <t>When we are creating the issue tree using demand-side methodology, we can use some standard parameters</t>
+    <t>Accounting basics</t>
   </si>
   <si>
-    <t>The parameters in question are
-- Age
-- Income
-- Location
-- Gender
-- Occupation
-- Country
-- Literacy rate
-- Mobile peneteration
-- Internet peneteration
-These allow us to segment the population correctly</t>
+    <t>Accounting is a language with its own set of rules. Journal entrying is the step through which we convert normal everyday transactions into accounting transactions</t>
   </si>
   <si>
-    <t>Demand Side Parameter selection</t>
+    <t>There are primarily 3 types of accounts
+- Personal : They represent a person / entity
+- Real : They represent asset / property of a business. Particularly, something that is tangible and part of business
+- Nominal : Generally covers intangible part of business like expense, loss, income, salary, purchase, gain etc. An abstract part of business
+## Rule of Debit / Credit
+| Type | Debit | Credit |
+| --- | --- | --- |
+| Personal | Recieved | Given |
+| Real | Inflow | Outflow |
+| Nominal | Expenses and losses | Income and gain |
+Note : All the above is seen from a perspective of a business. If someone gives money to business, it is counted as "money received by business"
+A few pointers
+- Cash is Real A/C
+- Bank is Personal A/C
+## Goods vs Assets
+- Assets are economically benefecial to business
+- Goods are things to be resold to someone else
+  - When we buy goods, we keep them in Purchases A/C
+  - When we sell goods, we keep them in Sales A/C
+## Debtor and Creditor
+- A debtor is a person or business that owes money to your company
+- A creditor is a person or business that your company owes money to
+## Samples
+The following table summarizes the accounting transactions discussed in the video, detailing the journal entry and the reasoning based on the Golden Rules of Accounting:
+markdown
+| Transaction | Journal Entry | Explanation |
+| :--- | :--- | :--- |
+| Started business with capital | Cash A/c Dr. To Capital A/c | Cash is an asset coming into the business (Real A/c: Debit what comes in); Capital represents the owner's investment (Personal A/c: Credit the giver). |
+| Purchased furniture for cash | Furniture A/c Dr. To Cash A/c | Furniture is an asset being acquired (Real A/c: Debit what comes in); Cash is an asset going out (Real A/c: Credit what goes out). |
+| Paid Rent | Rent A/c Dr. To Cash A/c | Rent is an operating expense (Nominal A/c: Debit all expenses); Cash is an asset leaving the business (Real A/c: Credit what goes out). |
+| Purchased goods via cheque | Purchase A/c Dr. To Bank A/c | Purchases are treated as expenses (Nominal A/c: Debit expenses); Bank is the giver of funds (Personal A/c: Credit the giver). |
+| Received cash from a debtor | Bank A/c Dr. To Debtor A/c | The bank account increases as it receives funds (Personal A/c: Debit the receiver); The debtor is the giver of the payment (Personal A/c: Credit the giver). |
+| Paid salary by cheque | Salary A/c Dr. To Bank A/c | Salary is an expense for the business (Nominal A/c: Debit expenses); The bank is the entity providing the payment (Personal A/c: Credit the giver). |
+| Received interest | Cash A/c Dr. To Interest Received A/c | Cash is an asset coming in (Real A/c: Debit what comes in); Interest received is an income (Nominal A/c: Credit all incomes/gains). |
+| Received cash from Amit | Cash A/c Dr. To Amit A/c | Cash is an asset coming in (Real A/c: Debit what comes in); Amit is the person paying the debt (Personal A/c: Credit the giver). |
+| Paid cash to Sujeet | Sujeet A/c Dr. To Cash A/c | Sujeet is the receiver of the payment (Personal A/c: Debit the receiver); Cash is an asset going out (Real A/c: Credit what goes out). |</t>
   </si>
 </sst>
 </file>
@@ -127,7 +152,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -269,22 +312,22 @@
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="Knowledge-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="12"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="secondRowStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="Compounding Reminder-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
     <tableStyle name="Master Quotes-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -302,8 +345,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Category"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Category" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Definition/Formula"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Explanation"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Pick Count"/>
@@ -564,21 +607,21 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="153" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -29425,7 +29468,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{23B6EFED-7FB9-447D-B22A-CEE89816EAB1}"/>
+      <autoFilter ref="A1:F23" xr:uid="{3739DB87-7162-4EAB-91C6-5083FB75FC1A}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42DDC7D-5994-46B3-AFFC-D4694E6FBEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E544F02D-C170-42C9-92FA-6A98F3A415E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="450" windowWidth="19320" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
@@ -46,54 +46,24 @@
     <t>Pick Count</t>
   </si>
   <si>
-    <t>Finance</t>
+    <t>MIS (Business and tech)</t>
   </si>
   <si>
-    <t>Journal Entries</t>
+    <t>IT Enablement</t>
   </si>
   <si>
-    <t>Accounting basics</t>
+    <t>Basics</t>
   </si>
   <si>
-    <t>Accounting is a language with its own set of rules. Journal entrying is the step through which we convert normal everyday transactions into accounting transactions</t>
+    <t>The core idea is that technology implementation must begin with business purpose, not with software or infrastructure. Decide the mission; next, choose the strategy to win; then define the moves; select the tools; and finally ensure the system can run them reliably</t>
   </si>
   <si>
-    <t>There are primarily 3 types of accounts
-- Personal : They represent a person / entity
-- Real : They represent asset / property of a business. Particularly, something that is tangible and part of business
-- Nominal : Generally covers intangible part of business like expense, loss, income, salary, purchase, gain etc. An abstract part of business
-## Rule of Debit / Credit
-| Type | Debit | Credit |
-| --- | --- | --- |
-| Personal | Recieved | Given |
-| Real | Inflow | Outflow |
-| Nominal | Expenses and losses | Income and gain |
-Note : All the above is seen from a perspective of a business. If someone gives money to business, it is counted as "money received by business"
-A few pointers
-- Cash is Real A/C
-- Bank is Personal A/C
-## Goods vs Assets
-- Assets are economically benefecial to business
-- Goods are things to be resold to someone else
-  - When we buy goods, we keep them in Purchases A/C
-  - When we sell goods, we keep them in Sales A/C
-## Debtor and Creditor
-- A debtor is a person or business that owes money to your company
-- A creditor is a person or business that your company owes money to
-## Samples
-The following table summarizes the accounting transactions discussed in the video, detailing the journal entry and the reasoning based on the Golden Rules of Accounting:
-markdown
-| Transaction | Journal Entry | Explanation |
-| :--- | :--- | :--- |
-| Started business with capital | Cash A/c Dr. To Capital A/c | Cash is an asset coming into the business (Real A/c: Debit what comes in); Capital represents the owner's investment (Personal A/c: Credit the giver). |
-| Purchased furniture for cash | Furniture A/c Dr. To Cash A/c | Furniture is an asset being acquired (Real A/c: Debit what comes in); Cash is an asset going out (Real A/c: Credit what goes out). |
-| Paid Rent | Rent A/c Dr. To Cash A/c | Rent is an operating expense (Nominal A/c: Debit all expenses); Cash is an asset leaving the business (Real A/c: Credit what goes out). |
-| Purchased goods via cheque | Purchase A/c Dr. To Bank A/c | Purchases are treated as expenses (Nominal A/c: Debit expenses); Bank is the giver of funds (Personal A/c: Credit the giver). |
-| Received cash from a debtor | Bank A/c Dr. To Debtor A/c | The bank account increases as it receives funds (Personal A/c: Debit the receiver); The debtor is the giver of the payment (Personal A/c: Credit the giver). |
-| Paid salary by cheque | Salary A/c Dr. To Bank A/c | Salary is an expense for the business (Nominal A/c: Debit expenses); The bank is the entity providing the payment (Personal A/c: Credit the giver). |
-| Received interest | Cash A/c Dr. To Interest Received A/c | Cash is an asset coming in (Real A/c: Debit what comes in); Interest received is an income (Nominal A/c: Credit all incomes/gains). |
-| Received cash from Amit | Cash A/c Dr. To Amit A/c | Cash is an asset coming in (Real A/c: Debit what comes in); Amit is the person paying the debt (Personal A/c: Credit the giver). |
-| Paid cash to Sujeet | Sujeet A/c Dr. To Cash A/c | Sujeet is the receiver of the payment (Personal A/c: Debit the receiver); Cash is an asset going out (Real A/c: Credit what goes out). |</t>
+    <t xml:space="preserve"> The following sequence must be kept in mind (in the exact same order) when we are implementing technology in business
+```
+Purpose -&gt; Theory of business -&gt; Process -&gt; Software -&gt; Infrastructure
+```
+&gt; Theory of business is the belief about how a company’s actions will create value for customers and achieve business goals
+For example, if a company wants to reduce customer delivery delays, its purpose is faster, more reliable delivery. Its theory of business might be that better demand forecasting and route planning will improve delivery performance. Its process would define how orders are prioritized, routes are assigned, and delays are handled. Only then should it select logistics software and build the required cloud infrastructure, databases, and networks.</t>
   </si>
 </sst>
 </file>
@@ -134,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -148,11 +118,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -312,22 +303,22 @@
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="Knowledge-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="13"/>
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="secondRowStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="secondRowStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="Compounding Reminder-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="10"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
     <tableStyle name="Master Quotes-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="5"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="secondRowStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" dxfId="4"/>
+      <tableStyleElement type="secondRowStripe" dxfId="3"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -345,9 +336,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Category" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Definition/Formula"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Category" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Definition/Formula" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Explanation"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Pick Count"/>
   </tableColumns>
@@ -607,7 +598,7 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="216.75" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -620,7 +611,7 @@
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4">
@@ -29468,12 +29459,13 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{3739DB87-7162-4EAB-91C6-5083FB75FC1A}"/>
+      <autoFilter ref="A1:F23" xr:uid="{9B0B46B8-9D16-4E87-BC2A-98696972814F}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E544F02D-C170-42C9-92FA-6A98F3A415E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681FDD50-4143-4FD6-BDFB-62E2D02E2225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Domain</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Pick Count</t>
   </si>
   <si>
-    <t>MIS (Business and tech)</t>
-  </si>
-  <si>
     <t>IT Enablement</t>
   </si>
   <si>
@@ -58,7 +55,21 @@
     <t>The core idea is that technology implementation must begin with business purpose, not with software or infrastructure. Decide the mission; next, choose the strategy to win; then define the moves; select the tools; and finally ensure the system can run them reliably</t>
   </si>
   <si>
-    <t xml:space="preserve"> The following sequence must be kept in mind (in the exact same order) when we are implementing technology in business
+    <t>Theory of firm</t>
+  </si>
+  <si>
+    <t>In "The Nature of the Firm" (1937), Coase asked why companies exist at all if markets are
+efficient. His answer: using the market has costs</t>
+  </si>
+  <si>
+    <t>A firm brings work inside when doing so costs less than buying it each time. Using the market has costs such as finding suppliers, negotiating, writing contracts, checking quality, enforcing agreements.
+Most transaction costs are really information costs: knowing who can do the job, at what price, and whether it was done well. So a firm is, at heart, a system for processing information.</t>
+  </si>
+  <si>
+    <t>Management Information Systems</t>
+  </si>
+  <si>
+    <t>The following sequence must be kept in mind (in the exact same order) when we are implementing technology in business
 ```
 Purpose -&gt; Theory of business -&gt; Process -&gt; Software -&gt; Infrastructure
 ```
@@ -70,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -83,13 +94,26 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -104,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -119,6 +143,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -333,7 +363,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F3">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="2"/>
@@ -598,21 +628,21 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="216.75" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="89.25" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -640,12 +670,24 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -29459,7 +29501,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{9B0B46B8-9D16-4E87-BC2A-98696972814F}"/>
+      <autoFilter ref="A1:F23" xr:uid="{44AD6E63-B9F9-4BFC-8585-BCB1C3DBA680}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681FDD50-4143-4FD6-BDFB-62E2D02E2225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11353B8-13B4-4B84-AC06-ACAAEFD6B1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,10 +58,6 @@
     <t>Theory of firm</t>
   </si>
   <si>
-    <t>In "The Nature of the Firm" (1937), Coase asked why companies exist at all if markets are
-efficient. His answer: using the market has costs</t>
-  </si>
-  <si>
     <t>A firm brings work inside when doing so costs less than buying it each time. Using the market has costs such as finding suppliers, negotiating, writing contracts, checking quality, enforcing agreements.
 Most transaction costs are really information costs: knowing who can do the job, at what price, and whether it was done well. So a firm is, at heart, a system for processing information.</t>
   </si>
@@ -75,6 +71,10 @@
 ```
 &gt; Theory of business is the belief about how a company’s actions will create value for customers and achieve business goals
 For example, if a company wants to reduce customer delivery delays, its purpose is faster, more reliable delivery. Its theory of business might be that better demand forecasting and route planning will improve delivery performance. Its process would define how orders are prioritized, routes are assigned, and delays are handled. Only then should it select logistics software and build the required cloud infrastructure, databases, and networks.</t>
+  </si>
+  <si>
+    <t>In 'The Nature of the Firm' (1937), Coase asked why companies exist at all if markets are
+efficient. His answer: using the market has costs</t>
   </si>
 </sst>
 </file>
@@ -630,7 +630,7 @@
     </row>
     <row r="2" spans="1:27" ht="89.25" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -639,10 +639,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="3" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>6</v>
@@ -683,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -29501,7 +29501,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{44AD6E63-B9F9-4BFC-8585-BCB1C3DBA680}"/>
+      <autoFilter ref="A1:F23" xr:uid="{B103FF60-9F24-4FE3-A27E-13BB3A4012B3}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11353B8-13B4-4B84-AC06-ACAAEFD6B1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C625B891-667D-4AA4-A7C1-05C8B949CAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$3</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Domain</t>
   </si>
@@ -75,6 +75,35 @@
   <si>
     <t>In 'The Nature of the Firm' (1937), Coase asked why companies exist at all if markets are
 efficient. His answer: using the market has costs</t>
+  </si>
+  <si>
+    <t>Theory of business and continuous evolution</t>
+  </si>
+  <si>
+    <t>Every organization runs on a set of assumptions, whether written down or not. The environment changes, so the theory of the business must be retested, processes redesigned and software rewritten. The companies that benefit are the ones that treat this as a permanent capability, not a one-time project.</t>
+  </si>
+  <si>
+    <t>The set of assumptions over the business runs on
+- Environment: who the customers are, what the market values, what technology and competitors are doing.
+- Mission: what results the organization exists to produce.
+- Core competencies: what it must be excellent at to deliver that mission.
+A sound theory fits reality, its three parts fit each other, it is understood across the organization, and it is tested constantly. When reality changes and the theory does not, even well-run companies decline.
+Since businesses environments and other variables change, any technology adoption should be considered as a lifetime project than a one-time thing</t>
+  </si>
+  <si>
+    <t>IT Interaction model</t>
+  </si>
+  <si>
+    <t>Software carries its own assumptions about how work should be done. The theory of the business should shape the technology, not the other way round.</t>
+  </si>
+  <si>
+    <t>The effects of an information system come from the interaction of three things
+- The system's features
+- The organizational context (strategy, structure, culture, business processes, existing IT) 
+- The implementation process. 
+Processes must be defined down to the atomic step
+"We provide great customer service" is a goal, not a process. A process is usable — and programmable — only when it is broken down level by level until each step is atomic: a single action with a clear actor, trigger, input, rule, output and time standard. A simple test: could a new employee perform the step with no further instruction? If not, keep going down.
+Technology turns processes into software running on robustinfrastructure Implementation means converting those atomic steps into programs, data and rules. The programs then run on infrastructure — networks, servers, data centres, backups. That infrastructure must be designed for the worst day, not the average one: peak demand, outages, disasters and crises.</t>
   </si>
 </sst>
 </file>
@@ -363,7 +392,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F5">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="2"/>
@@ -711,12 +740,24 @@
       <c r="AA3" s="1"/>
     </row>
     <row r="4" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -739,13 +780,25 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
-    <row r="5" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+    <row r="5" spans="1:27" ht="280.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C625B891-667D-4AA4-A7C1-05C8B949CAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB32C97C-E49F-45DD-935D-1642EBDABE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4065" yWindow="-15810" windowWidth="29040" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$5</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Domain</t>
   </si>
@@ -46,64 +46,73 @@
     <t>Pick Count</t>
   </si>
   <si>
-    <t>IT Enablement</t>
+    <t>General Management</t>
   </si>
   <si>
-    <t>Basics</t>
+    <t>SLA (Service Level Agreements)</t>
   </si>
   <si>
-    <t>The core idea is that technology implementation must begin with business purpose, not with software or infrastructure. Decide the mission; next, choose the strategy to win; then define the moves; select the tools; and finally ensure the system can run them reliably</t>
+    <t>Reliability</t>
   </si>
   <si>
-    <t>Theory of firm</t>
+    <t>An SLA stands for a Service Level Agreement. It is a formal, binding contract or agreement between a service provider and a customer (or between two internal departments) that defines the exact level of service expected to be delivered
+Anchored by four core pillars: a defined **scope of services**, measurable **performance metrics** (such as a 99.9% uptime baseline or tier-based helpdesk response deadlines), clearly outlined **provider and customer obligations**, and pre-negotiated **penalties and remedies** (like service credits or termination clauses).
+For complex ecosystems, organizations leverage a **multi-level SLA** to bundle various commitments into a single framework. This structured methodology breaks agreements down into three cohesive layers: **corporate-level policies** that apply globally, **customer-level agreements** customized for specific client groups, and **service-level metrics** tied directly to individual tools or assets. Together, these frameworks establish high accountability, streamline operations, and minimize redundancy across diverse workflows.</t>
   </si>
   <si>
-    <t>A firm brings work inside when doing so costs less than buying it each time. Using the market has costs such as finding suppliers, negotiating, writing contracts, checking quality, enforcing agreements.
-Most transaction costs are really information costs: knowing who can do the job, at what price, and whether it was done well. So a firm is, at heart, a system for processing information.</t>
-  </si>
-  <si>
-    <t>Management Information Systems</t>
-  </si>
-  <si>
-    <t>The following sequence must be kept in mind (in the exact same order) when we are implementing technology in business
+    <t>An SLA typically outlines:
+- **Scope of Services:** What is included and what is excluded.
+- **Performance Metrics:** Measurable targets such as system uptime (e.g., 99.9%), response times for support tickets, and resolution deadlines.
+- **Responsibilities:** What both the provider and the customer must do to maintain the service.
+- **Penalties and Remedies:** What happens if the provider fails to meet the agreed standards, such as service credits, fee discounts, or a right to terminate the contract. 
+```mermaid
+mindmap
+  root((Core Components&lt;br&gt;of an SLA))
+    **Scope of Services**
+      What is included
+      What is excluded
+    **Performance Metrics**
+      System uptime targets&lt;br&gt;e.g., 99.9%
+      Support ticket&lt;br&gt;response times
+      Resolution deadlines
+    **Responsibilities**
+      Provider obligations
+      Customer obligations
+      Maintenance protocols
+    **Penalties and Remedies**
+      Service credits
+      Fee discounts
+      Termination rights
 ```
-Purpose -&gt; Theory of business -&gt; Process -&gt; Software -&gt; Infrastructure
-```
-&gt; Theory of business is the belief about how a company’s actions will create value for customers and achieve business goals
-For example, if a company wants to reduce customer delivery delays, its purpose is faster, more reliable delivery. Its theory of business might be that better demand forecasting and route planning will improve delivery performance. Its process would define how orders are prioritized, routes are assigned, and delays are handled. Only then should it select logistics software and build the required cloud infrastructure, databases, and networks.</t>
-  </si>
-  <si>
-    <t>In 'The Nature of the Firm' (1937), Coase asked why companies exist at all if markets are
-efficient. His answer: using the market has costs</t>
-  </si>
-  <si>
-    <t>Theory of business and continuous evolution</t>
-  </si>
-  <si>
-    <t>Every organization runs on a set of assumptions, whether written down or not. The environment changes, so the theory of the business must be retested, processes redesigned and software rewritten. The companies that benefit are the ones that treat this as a permanent capability, not a one-time project.</t>
-  </si>
-  <si>
-    <t>The set of assumptions over the business runs on
-- Environment: who the customers are, what the market values, what technology and competitors are doing.
-- Mission: what results the organization exists to produce.
-- Core competencies: what it must be excellent at to deliver that mission.
-A sound theory fits reality, its three parts fit each other, it is understood across the organization, and it is tested constantly. When reality changes and the theory does not, even well-run companies decline.
-Since businesses environments and other variables change, any technology adoption should be considered as a lifetime project than a one-time thing</t>
-  </si>
-  <si>
-    <t>IT Interaction model</t>
-  </si>
-  <si>
-    <t>Software carries its own assumptions about how work should be done. The theory of the business should shape the technology, not the other way round.</t>
-  </si>
-  <si>
-    <t>The effects of an information system come from the interaction of three things
-- The system's features
-- The organizational context (strategy, structure, culture, business processes, existing IT) 
-- The implementation process. 
-Processes must be defined down to the atomic step
-"We provide great customer service" is a goal, not a process. A process is usable — and programmable — only when it is broken down level by level until each step is atomic: a single action with a clear actor, trigger, input, rule, output and time standard. A simple test: could a new employee perform the step with no further instruction? If not, keep going down.
-Technology turns processes into software running on robustinfrastructure Implementation means converting those atomic steps into programs, data and rules. The programs then run on infrastructure — networks, servers, data centres, backups. That infrastructure must be designed for the worst day, not the average one: peak demand, outages, disasters and crises.</t>
+Common Types of SLAs
+- **Customer SLA:** An agreement between a service provider and an external client.
+- **Internal SLA:** An agreement between different teams or departments within the same company (e.g., a sales team and a marketing team).
+- **Multi-Level SLA:** A layered agreement that covers various customer segments, multiple support tiers, or a mix of internal and external stakeholders. 
+### Example 1: Cloud Uptime Example (IT &amp; SaaS)
+An enterprise cloud hosting provider (like Amazon Web Services or Microsoft Azure) signs an agreement with an online retail company.
+- **The Promise:** The cloud server will maintain **99.9% uptime** each month.
+- **The Math:** 99.9% uptime allows for roughly 43.8 minutes of unplanned downtime per month. If the server crashes for 5 hours due to a provider failure, they have breached the SLA.
+- **The Penalty / Remedy:** The agreement states that if uptime drops between 99.0% and 99.8%, the customer gets a **10% service credit** on their next monthly bill. If it drops below 95%, they receive a **50% to 100% refund/credit** for that month.
+### Example 2 : Helpdesk Response &amp; Resolution Example (Internal or B2B IT Support)
+An internal IT department or an external managed service provider (MSP) supports a company's employees. The SLA sets strict reaction times based on how badly a problem hurts the business:
+- **Severity 1 (Critical – e.g., entire office internet is down):**
+    - _Response Time:_ Within **15 minutes** (an engineer must acknowledge and start working).
+    - _Resolution Target:_ Within **4 hours**.
+- **Severity 3 (Low – e.g., a printer isn’t connecting on the 2nd floor):**
+    - _Response Time:_ Within **4 business hours**.
+    - _Resolution Target:_ Within **2 to 5 business days**.
+- **The Remedy:** If Severity 1 issues regularly miss the 4-hour fix window without a valid excuse, the contract allows the client to escalate to senior management or withhold a portion of the monthly retainer.
+### Example 3 : Customer Service / E-Commerce Chatbot Example
+An online banking or retail platform guarantees customer service quality for incoming queries:
+- **First-Response Time:** 95% of live-chat or email queries must receive a human or automated response within **2 minutes**.
+- **First-Contact Resolution (FCR):** At least **75% of customer issues** must be completely solved on the first interaction without needing a callback or transfer.
+- **Abandonment Rate:** Fewer than **3% of callers** should hang up before reaching an agent.
+- **The Remedy:** If the provider misses these metrics for two consecutive quarters, the business can penalize the vendor or put the contract up for re-bidding.
+4. Multi-Level SaaS Tier Example (Corporate, Customer, and Service)
+A software company sells a project-management tool to a large hospital network:
+- **Corporate Level:** Applies to everyone—all users must connect using **TLS 1.2+ encryption** and comply with local data-privacy laws.
+- **Customer Level:** Applies specifically to the Hospital Group—they receive a dedicated Account Manager and **24/7 priority phone support**.
+- **Service Level:** Applies to the specific Radiology Imaging module inside the software—it guarantees a **99.99% uptime** and database search response times under **1 second**.</t>
   </si>
 </sst>
 </file>
@@ -121,28 +130,23 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -157,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -169,12 +173,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -392,7 +390,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="2"/>
@@ -657,18 +655,18 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="89.25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>10</v>
@@ -699,24 +697,12 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -740,24 +726,12 @@
       <c r="AA3" s="1"/>
     </row>
     <row r="4" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -780,25 +754,13 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
-    <row r="5" spans="1:27" ht="280.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
+    <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -28980,13 +28942,7 @@
       <c r="Z976" s="1"/>
       <c r="AA976" s="1"/>
     </row>
-    <row r="977" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A977" s="1"/>
-      <c r="B977" s="1"/>
-      <c r="C977" s="1"/>
-      <c r="D977" s="1"/>
-      <c r="E977" s="1"/>
-      <c r="F977" s="1"/>
+    <row r="977" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G977" s="1"/>
       <c r="H977" s="1"/>
       <c r="I977" s="1"/>
@@ -29009,13 +28965,7 @@
       <c r="Z977" s="1"/>
       <c r="AA977" s="1"/>
     </row>
-    <row r="978" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A978" s="1"/>
-      <c r="B978" s="1"/>
-      <c r="C978" s="1"/>
-      <c r="D978" s="1"/>
-      <c r="E978" s="1"/>
-      <c r="F978" s="1"/>
+    <row r="978" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G978" s="1"/>
       <c r="H978" s="1"/>
       <c r="I978" s="1"/>
@@ -29038,13 +28988,7 @@
       <c r="Z978" s="1"/>
       <c r="AA978" s="1"/>
     </row>
-    <row r="979" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A979" s="1"/>
-      <c r="B979" s="1"/>
-      <c r="C979" s="1"/>
-      <c r="D979" s="1"/>
-      <c r="E979" s="1"/>
-      <c r="F979" s="1"/>
+    <row r="979" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G979" s="1"/>
       <c r="H979" s="1"/>
       <c r="I979" s="1"/>
@@ -29067,7 +29011,7 @@
       <c r="Z979" s="1"/>
       <c r="AA979" s="1"/>
     </row>
-    <row r="980" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="980" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G980" s="1"/>
       <c r="H980" s="1"/>
       <c r="I980" s="1"/>
@@ -29090,7 +29034,7 @@
       <c r="Z980" s="1"/>
       <c r="AA980" s="1"/>
     </row>
-    <row r="981" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="981" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G981" s="1"/>
       <c r="H981" s="1"/>
       <c r="I981" s="1"/>
@@ -29113,7 +29057,7 @@
       <c r="Z981" s="1"/>
       <c r="AA981" s="1"/>
     </row>
-    <row r="982" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="982" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G982" s="1"/>
       <c r="H982" s="1"/>
       <c r="I982" s="1"/>
@@ -29136,7 +29080,7 @@
       <c r="Z982" s="1"/>
       <c r="AA982" s="1"/>
     </row>
-    <row r="983" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="983" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G983" s="1"/>
       <c r="H983" s="1"/>
       <c r="I983" s="1"/>
@@ -29159,7 +29103,7 @@
       <c r="Z983" s="1"/>
       <c r="AA983" s="1"/>
     </row>
-    <row r="984" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="984" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G984" s="1"/>
       <c r="H984" s="1"/>
       <c r="I984" s="1"/>
@@ -29182,7 +29126,7 @@
       <c r="Z984" s="1"/>
       <c r="AA984" s="1"/>
     </row>
-    <row r="985" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="985" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G985" s="1"/>
       <c r="H985" s="1"/>
       <c r="I985" s="1"/>
@@ -29205,7 +29149,7 @@
       <c r="Z985" s="1"/>
       <c r="AA985" s="1"/>
     </row>
-    <row r="986" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="986" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G986" s="1"/>
       <c r="H986" s="1"/>
       <c r="I986" s="1"/>
@@ -29228,7 +29172,7 @@
       <c r="Z986" s="1"/>
       <c r="AA986" s="1"/>
     </row>
-    <row r="987" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="987" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G987" s="1"/>
       <c r="H987" s="1"/>
       <c r="I987" s="1"/>
@@ -29251,7 +29195,7 @@
       <c r="Z987" s="1"/>
       <c r="AA987" s="1"/>
     </row>
-    <row r="988" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="988" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G988" s="1"/>
       <c r="H988" s="1"/>
       <c r="I988" s="1"/>
@@ -29274,7 +29218,7 @@
       <c r="Z988" s="1"/>
       <c r="AA988" s="1"/>
     </row>
-    <row r="989" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="989" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G989" s="1"/>
       <c r="H989" s="1"/>
       <c r="I989" s="1"/>
@@ -29297,7 +29241,7 @@
       <c r="Z989" s="1"/>
       <c r="AA989" s="1"/>
     </row>
-    <row r="990" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="990" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G990" s="1"/>
       <c r="H990" s="1"/>
       <c r="I990" s="1"/>
@@ -29320,7 +29264,7 @@
       <c r="Z990" s="1"/>
       <c r="AA990" s="1"/>
     </row>
-    <row r="991" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="991" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G991" s="1"/>
       <c r="H991" s="1"/>
       <c r="I991" s="1"/>
@@ -29343,7 +29287,7 @@
       <c r="Z991" s="1"/>
       <c r="AA991" s="1"/>
     </row>
-    <row r="992" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="992" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="G992" s="1"/>
       <c r="H992" s="1"/>
       <c r="I992" s="1"/>
@@ -29554,7 +29498,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{B103FF60-9F24-4FE3-A27E-13BB3A4012B3}"/>
+      <autoFilter ref="A1:F23" xr:uid="{5817FDCF-08EC-44F6-84BD-8A54B3224FD6}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB32C97C-E49F-45DD-935D-1642EBDABE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B454394-DB03-43B8-B9B5-5A1086EE51CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="-15810" windowWidth="29040" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,12 +55,12 @@
     <t>Reliability</t>
   </si>
   <si>
-    <t>An SLA stands for a Service Level Agreement. It is a formal, binding contract or agreement between a service provider and a customer (or between two internal departments) that defines the exact level of service expected to be delivered
-Anchored by four core pillars: a defined **scope of services**, measurable **performance metrics** (such as a 99.9% uptime baseline or tier-based helpdesk response deadlines), clearly outlined **provider and customer obligations**, and pre-negotiated **penalties and remedies** (like service credits or termination clauses).
-For complex ecosystems, organizations leverage a **multi-level SLA** to bundle various commitments into a single framework. This structured methodology breaks agreements down into three cohesive layers: **corporate-level policies** that apply globally, **customer-level agreements** customized for specific client groups, and **service-level metrics** tied directly to individual tools or assets. Together, these frameworks establish high accountability, streamline operations, and minimize redundancy across diverse workflows.</t>
+    <t>An SLA stands for a Service Level Agreement. It is a formal, binding contract or agreement between a service provider and a customer (or between two internal departments) that defines the exact level of service expected to be delivered</t>
   </si>
   <si>
-    <t>An SLA typically outlines:
+    <t>Anchored by four core pillars: a defined **scope of services**, measurable **performance metrics** (such as a 99.9% uptime baseline or tier-based helpdesk response deadlines), clearly outlined **provider and customer obligations**, and pre-negotiated **penalties and remedies** (like service credits or termination clauses).
+For complex ecosystems, organizations leverage a **multi-level SLA** to bundle various commitments into a single framework. This structured methodology breaks agreements down into three cohesive layers: **corporate-level policies** that apply globally, **customer-level agreements** customized for specific client groups, and **service-level metrics** tied directly to individual tools or assets. Together, these frameworks establish high accountability, streamline operations, and minimize redundancy across diverse workflows.
+An SLA typically outlines:
 - **Scope of Services:** What is included and what is excluded.
 - **Performance Metrics:** Measurable targets such as system uptime (e.g., 99.9%), response times for support tickets, and resolution deadlines.
 - **Responsibilities:** What both the provider and the customer must do to maintain the service.
@@ -176,13 +176,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -360,22 +363,22 @@
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="Knowledge-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="14"/>
-      <tableStyleElement type="headerRow" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="secondRowStripe" dxfId="11"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
     <tableStyle name="Compounding Reminder-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="10"/>
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
-      <tableStyleElement type="secondRowStripe" dxfId="7"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
     <tableStyle name="Master Quotes-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -393,10 +396,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Category" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Definition/Formula" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Explanation"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Category" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Definition/Formula" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Explanation" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Pick Count"/>
   </tableColumns>
   <tableStyleInfo name="Knowledge-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -611,7 +614,7 @@
     <col min="2" max="2" width="15.59765625" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="27.46484375" customWidth="1"/>
-    <col min="5" max="5" width="59.59765625" customWidth="1"/>
+    <col min="5" max="5" width="84.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B454394-DB03-43B8-B9B5-5A1086EE51CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484FD103-E023-414D-922D-9956FC34E85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="-15810" windowWidth="29040" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Domain</t>
   </si>
@@ -114,6 +114,31 @@
 - **Customer Level:** Applies specifically to the Hospital Group—they receive a dedicated Account Manager and **24/7 priority phone support**.
 - **Service Level:** Applies to the specific Radiology Imaging module inside the software—it guarantees a **99.99% uptime** and database search response times under **1 second**.</t>
   </si>
+  <si>
+    <t>Working with yourself</t>
+  </si>
+  <si>
+    <t>LEGO Method of bagging tasks</t>
+  </si>
+  <si>
+    <t>Productivity</t>
+  </si>
+  <si>
+    <t>When you look at a major project as one giant task (like "Write Master's Thesis" or "Clean the Entire House"), your brain experiences cognitive overload. This triggers anxiety, which leads directly to procrastination. Accept that you cannot build the final structure in a single sitting.
+Divide your massive project into highly specific, sequential phases—just like LEGO bags. Each "bag" should represent a micro-milestone that feels completely manageable.
+Instead of: "Prepare quarterly tax report."
+- Bag 1: Gather all receipts from Q3.
+- Bag 2: Log receipts into the spreadsheet.
+- Bag 3: Calculate total expenses.
+### Open Only One Bag at a Time
+When you sit down to work, your only objective is to finish the current numbered bag. Clear your workspace of everything else. Do not worry about Bag 4 while you are working on Bag 2. This hyper-focus lowers the barrier to entry, making it much easier to simply start.
+### Celebrate the Micro-Builds
+Modern LEGO sets give you a sense of accomplishment quickly; finishing Bag 1 usually rewards you with a completed minifig or the base of a vehicle. In your work, acknowledge the completion of each small bag. This releases dopamine, building the positive momentum you need to open the next bag.
+https://lnkd.in/p/d_qAJzJS</t>
+  </si>
+  <si>
+    <t>The LEGO Method for overcoming procrastination is a productivity strategy based on how modern LEGO sets are packaged: breaking a massive, overwhelming project into small, numbered bags that can be completed one at a time.</t>
+  </si>
 </sst>
 </file>
 
@@ -161,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -174,6 +199,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -393,7 +421,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F3">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="3"/>
@@ -612,7 +640,7 @@
   <cols>
     <col min="1" max="1" width="10.3984375" customWidth="1"/>
     <col min="2" max="2" width="15.59765625" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="3" max="3" width="11.53125" customWidth="1"/>
     <col min="4" max="4" width="27.46484375" customWidth="1"/>
     <col min="5" max="5" width="84.53125" customWidth="1"/>
   </cols>
@@ -671,7 +699,7 @@
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4">
@@ -699,12 +727,22 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+    <row r="3" spans="1:27" ht="293.25" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -29504,10 +29542,13 @@
       <autoFilter ref="A1:F23" xr:uid="{5817FDCF-08EC-44F6-84BD-8A54B3224FD6}"/>
     </customSheetView>
   </customSheetViews>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" display="https://lnkd.in/p/d_qAJzJS" xr:uid="{A9135A7B-4C63-48BD-956F-3AD9FF86D3AC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484FD103-E023-414D-922D-9956FC34E85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9767B3E-1157-4FBF-BBDC-0C098BB004D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="-15810" windowWidth="29040" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,30 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$3</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$4</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <customWorkbookViews>
     <customWorkbookView name="View -&gt; Group by Pick Count" guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Domain</t>
   </si>
@@ -139,12 +152,94 @@
   <si>
     <t>The LEGO Method for overcoming procrastination is a productivity strategy based on how modern LEGO sets are packaged: breaking a massive, overwhelming project into small, numbered bags that can be completed one at a time.</t>
   </si>
+  <si>
+    <t>Math and Statistics</t>
+  </si>
+  <si>
+    <t>Cluster vs Stratified sampling</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>Sampling is the process of selecting a subset of a population to draw conclusions about the whole. It saves time, cost, and effort while making research practical. The key methods include stratified sampling, which takes samples from every group; cluster sampling, which studies selected groups; and multi-stage sampling, which selects samples in multiple steps, from larger groups to smaller units.</t>
+  </si>
+  <si>
+    <t>## Overview
+Sampling is the process of selecting a subset of a population to draw conclusions about the whole. It saves time, cost, and effort while making research practical. The key methods include stratified sampling, which takes samples from every group; cluster sampling, which studies selected groups; and multi-stage sampling, which selects samples in multiple steps, from larger groups to smaller units.
+## Explanation
+Cluster sampling and stratified sampling differ mainly in what you select and why you select it. In stratified sampling, you divide the population into groups and sample from every group, while in cluster sampling, you divide the population into groups and select only some groups for study.
+Imagine XLRI has 1,000 students across different programs and years. You want to survey students about campus life, so you need a way to select a manageable sample.
+### Stratified sampling
+Take some students from every group. Divide the students into **strata**, such as `BM (Business Management)`, `HRM (Human Resource Management)`, and other programs, then randomly select students from each group. This ensures every program is represented in your sample.
+```mermaid
+flowchart TD
+    A["All MBA Students"] --&gt; B["BM"]
+    A --&gt; C["HRM"]
+    A --&gt; D["Other Programs"]
+    B --&gt; E["Randomly Select Students"]
+    C --&gt; F["Randomly Select Students"]
+    D --&gt; G["Randomly Select Students"]
+    E --&gt; H["Final Sample"]
+    F --&gt; H
+    G --&gt; H
+    classDef group fill:#DCEBFA,stroke:#3973AC,color:#163A5C
+    classDef result fill:#DDF3E4,stroke:#39845A,color:#174D2D
+    class B,C,D,E,F,G group
+    class H result
+```
+### Cluster sampling
+Divide the students into clusters, such as year (first year or second year), sections etc. You survey students in those selected sections rather than sampling from every section. Ideally, each cluster reflects the wider population. 
+```mermaid
+flowchart TD
+    A["All MBA Students"] --&gt; B["Section 1"]
+    A --&gt; C["Section 2"]
+    A --&gt; D["Section 3"]
+    A --&gt; E["Section 4"]
+    B --&gt; F["Selected"]
+    D --&gt; F
+    F --&gt; G["Survey All Students in Selected Sections"]
+    G --&gt; H["Final Sample"]
+    classDef group fill:#DCEBFA,stroke:#3973AC,color:#163A5C
+    classDef selected fill:#FBE7C6,stroke:#B7791F,color:#704214
+    classDef result fill:#DDF3E4,stroke:#39845A,color:#174D2D
+    class B,C,D,E group
+    class F,G selected
+    class H result
+```
+### Summary of these methods
+| Basis          | Stratified sampling                         | Cluster sampling                                    |
+| -------------- | ------------------------------------------- | --------------------------------------------------- |
+| Selection      | Some members from every stratum             | Some clusters from the population                   |
+| Groups         | Similar members within each stratum         | Ideally, each cluster reflects the wider population |
+| Main objective | Ensure representation and improve precision | Reduce cost and effort                              |
+| Example        | Students sampled from every program         | A few tutorial sections selected                    |
+&gt; [!tip]
+&gt; Stratified means all groups represented; cluster means some groups selected
+### Cluster Sampling Iteratively
+After creating clusters, we can further create clusters to pinpoint the criteria of people we need. Imagine you want to survey MBA students across India, but you cannot visit every college, so you randomly select 3 states, then 4 colleges in each state, then 2 classes in each college, and finally 10 students from each class. You have selected your sample through four stages, giving you \(3 \times 4 \times 2 \times 10 = 240\) students.
+```mermaid
+flowchart TD
+    A["MBA Students Across India"]
+    A --&gt; B["Stage 1: Select 3 States"]
+    B --&gt; C["Stage 2: Select 4 Colleges per State"]
+    C --&gt; D["Stage 3: Select 2 Classes per College"]
+    D --&gt; E["Stage 4: Select 10 Students per Class"]
+    E --&gt; F["Final Sample: 240 Students"]
+    style A fill:#E5E7EB,stroke:#6B7280,color:#111827
+    style B fill:#DBEAFE,stroke:#2563EB,color:#1E3A8A
+    style C fill:#D1FAE5,stroke:#059669,color:#064E3B
+    style D fill:#FEF3C7,stroke:#D97706,color:#78350F
+    style E fill:#F3E8FF,stroke:#9333EA,color:#581C87
+    style F fill:#DCFCE7,stroke:#16A34A,color:#14532D
+```</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -163,6 +258,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -186,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -205,6 +306,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -421,7 +528,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F4">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="3"/>
@@ -766,12 +873,22 @@
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
     </row>
-    <row r="4" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+    <row r="4" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9767B3E-1157-4FBF-BBDC-0C098BB004D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8CD346-F24A-49FB-90ED-584C6B47DC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="-15810" windowWidth="29040" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$4</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Domain</t>
   </si>
@@ -59,100 +59,6 @@
     <t>Pick Count</t>
   </si>
   <si>
-    <t>General Management</t>
-  </si>
-  <si>
-    <t>SLA (Service Level Agreements)</t>
-  </si>
-  <si>
-    <t>Reliability</t>
-  </si>
-  <si>
-    <t>An SLA stands for a Service Level Agreement. It is a formal, binding contract or agreement between a service provider and a customer (or between two internal departments) that defines the exact level of service expected to be delivered</t>
-  </si>
-  <si>
-    <t>Anchored by four core pillars: a defined **scope of services**, measurable **performance metrics** (such as a 99.9% uptime baseline or tier-based helpdesk response deadlines), clearly outlined **provider and customer obligations**, and pre-negotiated **penalties and remedies** (like service credits or termination clauses).
-For complex ecosystems, organizations leverage a **multi-level SLA** to bundle various commitments into a single framework. This structured methodology breaks agreements down into three cohesive layers: **corporate-level policies** that apply globally, **customer-level agreements** customized for specific client groups, and **service-level metrics** tied directly to individual tools or assets. Together, these frameworks establish high accountability, streamline operations, and minimize redundancy across diverse workflows.
-An SLA typically outlines:
-- **Scope of Services:** What is included and what is excluded.
-- **Performance Metrics:** Measurable targets such as system uptime (e.g., 99.9%), response times for support tickets, and resolution deadlines.
-- **Responsibilities:** What both the provider and the customer must do to maintain the service.
-- **Penalties and Remedies:** What happens if the provider fails to meet the agreed standards, such as service credits, fee discounts, or a right to terminate the contract. 
-```mermaid
-mindmap
-  root((Core Components&lt;br&gt;of an SLA))
-    **Scope of Services**
-      What is included
-      What is excluded
-    **Performance Metrics**
-      System uptime targets&lt;br&gt;e.g., 99.9%
-      Support ticket&lt;br&gt;response times
-      Resolution deadlines
-    **Responsibilities**
-      Provider obligations
-      Customer obligations
-      Maintenance protocols
-    **Penalties and Remedies**
-      Service credits
-      Fee discounts
-      Termination rights
-```
-Common Types of SLAs
-- **Customer SLA:** An agreement between a service provider and an external client.
-- **Internal SLA:** An agreement between different teams or departments within the same company (e.g., a sales team and a marketing team).
-- **Multi-Level SLA:** A layered agreement that covers various customer segments, multiple support tiers, or a mix of internal and external stakeholders. 
-### Example 1: Cloud Uptime Example (IT &amp; SaaS)
-An enterprise cloud hosting provider (like Amazon Web Services or Microsoft Azure) signs an agreement with an online retail company.
-- **The Promise:** The cloud server will maintain **99.9% uptime** each month.
-- **The Math:** 99.9% uptime allows for roughly 43.8 minutes of unplanned downtime per month. If the server crashes for 5 hours due to a provider failure, they have breached the SLA.
-- **The Penalty / Remedy:** The agreement states that if uptime drops between 99.0% and 99.8%, the customer gets a **10% service credit** on their next monthly bill. If it drops below 95%, they receive a **50% to 100% refund/credit** for that month.
-### Example 2 : Helpdesk Response &amp; Resolution Example (Internal or B2B IT Support)
-An internal IT department or an external managed service provider (MSP) supports a company's employees. The SLA sets strict reaction times based on how badly a problem hurts the business:
-- **Severity 1 (Critical – e.g., entire office internet is down):**
-    - _Response Time:_ Within **15 minutes** (an engineer must acknowledge and start working).
-    - _Resolution Target:_ Within **4 hours**.
-- **Severity 3 (Low – e.g., a printer isn’t connecting on the 2nd floor):**
-    - _Response Time:_ Within **4 business hours**.
-    - _Resolution Target:_ Within **2 to 5 business days**.
-- **The Remedy:** If Severity 1 issues regularly miss the 4-hour fix window without a valid excuse, the contract allows the client to escalate to senior management or withhold a portion of the monthly retainer.
-### Example 3 : Customer Service / E-Commerce Chatbot Example
-An online banking or retail platform guarantees customer service quality for incoming queries:
-- **First-Response Time:** 95% of live-chat or email queries must receive a human or automated response within **2 minutes**.
-- **First-Contact Resolution (FCR):** At least **75% of customer issues** must be completely solved on the first interaction without needing a callback or transfer.
-- **Abandonment Rate:** Fewer than **3% of callers** should hang up before reaching an agent.
-- **The Remedy:** If the provider misses these metrics for two consecutive quarters, the business can penalize the vendor or put the contract up for re-bidding.
-4. Multi-Level SaaS Tier Example (Corporate, Customer, and Service)
-A software company sells a project-management tool to a large hospital network:
-- **Corporate Level:** Applies to everyone—all users must connect using **TLS 1.2+ encryption** and comply with local data-privacy laws.
-- **Customer Level:** Applies specifically to the Hospital Group—they receive a dedicated Account Manager and **24/7 priority phone support**.
-- **Service Level:** Applies to the specific Radiology Imaging module inside the software—it guarantees a **99.99% uptime** and database search response times under **1 second**.</t>
-  </si>
-  <si>
-    <t>Working with yourself</t>
-  </si>
-  <si>
-    <t>LEGO Method of bagging tasks</t>
-  </si>
-  <si>
-    <t>Productivity</t>
-  </si>
-  <si>
-    <t>When you look at a major project as one giant task (like "Write Master's Thesis" or "Clean the Entire House"), your brain experiences cognitive overload. This triggers anxiety, which leads directly to procrastination. Accept that you cannot build the final structure in a single sitting.
-Divide your massive project into highly specific, sequential phases—just like LEGO bags. Each "bag" should represent a micro-milestone that feels completely manageable.
-Instead of: "Prepare quarterly tax report."
-- Bag 1: Gather all receipts from Q3.
-- Bag 2: Log receipts into the spreadsheet.
-- Bag 3: Calculate total expenses.
-### Open Only One Bag at a Time
-When you sit down to work, your only objective is to finish the current numbered bag. Clear your workspace of everything else. Do not worry about Bag 4 while you are working on Bag 2. This hyper-focus lowers the barrier to entry, making it much easier to simply start.
-### Celebrate the Micro-Builds
-Modern LEGO sets give you a sense of accomplishment quickly; finishing Bag 1 usually rewards you with a completed minifig or the base of a vehicle. In your work, acknowledge the completion of each small bag. This releases dopamine, building the positive momentum you need to open the next bag.
-https://lnkd.in/p/d_qAJzJS</t>
-  </si>
-  <si>
-    <t>The LEGO Method for overcoming procrastination is a productivity strategy based on how modern LEGO sets are packaged: breaking a massive, overwhelming project into small, numbered bags that can be completed one at a time.</t>
-  </si>
-  <si>
     <t>Math and Statistics</t>
   </si>
   <si>
@@ -165,10 +71,7 @@
     <t>Sampling is the process of selecting a subset of a population to draw conclusions about the whole. It saves time, cost, and effort while making research practical. The key methods include stratified sampling, which takes samples from every group; cluster sampling, which studies selected groups; and multi-stage sampling, which selects samples in multiple steps, from larger groups to smaller units.</t>
   </si>
   <si>
-    <t>## Overview
-Sampling is the process of selecting a subset of a population to draw conclusions about the whole. It saves time, cost, and effort while making research practical. The key methods include stratified sampling, which takes samples from every group; cluster sampling, which studies selected groups; and multi-stage sampling, which selects samples in multiple steps, from larger groups to smaller units.
-## Explanation
-Cluster sampling and stratified sampling differ mainly in what you select and why you select it. In stratified sampling, you divide the population into groups and sample from every group, while in cluster sampling, you divide the population into groups and select only some groups for study.
+    <t>Cluster sampling and stratified sampling differ mainly in what you select and why you select it. In stratified sampling, you divide the population into groups and sample from every group, while in cluster sampling, you divide the population into groups and select only some groups for study.
 Imagine XLRI has 1,000 students across different programs and years. You want to survey students about campus life, so you need a way to select a manageable sample.
 ### Stratified sampling
 Take some students from every group. Divide the students into **strata**, such as `BM (Business Management)`, `HRM (Human Resource Management)`, and other programs, then randomly select students from each group. This ensures every program is represented in your sample.
@@ -239,7 +142,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -249,13 +152,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -287,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -299,18 +195,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -528,7 +415,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="3"/>
@@ -794,24 +681,22 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -834,22 +719,12 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" ht="293.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
-      </c>
+    <row r="3" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -873,22 +748,12 @@
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
     </row>
-    <row r="4" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>20</v>
-      </c>
+    <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -29043,12 +28908,6 @@
       <c r="AA974" s="1"/>
     </row>
     <row r="975" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A975" s="1"/>
-      <c r="B975" s="1"/>
-      <c r="C975" s="1"/>
-      <c r="D975" s="1"/>
-      <c r="E975" s="1"/>
-      <c r="F975" s="1"/>
       <c r="G975" s="1"/>
       <c r="H975" s="1"/>
       <c r="I975" s="1"/>
@@ -29072,12 +28931,6 @@
       <c r="AA975" s="1"/>
     </row>
     <row r="976" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A976" s="1"/>
-      <c r="B976" s="1"/>
-      <c r="C976" s="1"/>
-      <c r="D976" s="1"/>
-      <c r="E976" s="1"/>
-      <c r="F976" s="1"/>
       <c r="G976" s="1"/>
       <c r="H976" s="1"/>
       <c r="I976" s="1"/>
@@ -29659,13 +29512,10 @@
       <autoFilter ref="A1:F23" xr:uid="{5817FDCF-08EC-44F6-84BD-8A54B3224FD6}"/>
     </customSheetView>
   </customSheetViews>
-  <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" display="https://lnkd.in/p/d_qAJzJS" xr:uid="{A9135A7B-4C63-48BD-956F-3AD9FF86D3AC}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8CD346-F24A-49FB-90ED-584C6B47DC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD07C06C-80A5-4F0C-93CE-14539FACF9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="-15810" windowWidth="29040" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Domain</t>
   </si>
@@ -136,6 +136,45 @@
     style E fill:#F3E8FF,stroke:#9333EA,color:#581C87
     style F fill:#DCFCE7,stroke:#16A34A,color:#14532D
 ```</t>
+  </si>
+  <si>
+    <t>Economics</t>
+  </si>
+  <si>
+    <t>Factors of production</t>
+  </si>
+  <si>
+    <t>Macroeconomics</t>
+  </si>
+  <si>
+    <t>An economy can be understood as a system in which Land, Labour, Capital, and Entrepreneurship work together to produce goods and services, generate income, and improve people's standard of living. Land provides the natural resources, labour provides the workers doing the work, capital provides the tools and equipment, and entrepreneurship acts like the strategist who brings everything together. When these factors combine efficiently, the economy can produce more output, create jobs, and grow its GDP.</t>
+  </si>
+  <si>
+    <t>### GDP
+It is the total monetary value of all final goods and services produced within a country's borders in a specific time frame (usually a year). It is the ultimate scoreboard for a country, measuring its economic size, output, and overall health.
+Economists created different types of GDP to separate the illusion of rising prices from actual, tangible growth in production. If one thing that costed 100 previous year but now costs 110, it's not that the economy got bigger, just that the money lost its value $\implies$ you pay more for the same thing as before
+- **Nominal GDP**: This is GDP measured at current market prices. It includes the effects of inflation
+- **Real GDP**: Inflation-adjusted score. Calculates the value of goods using the prices from a fixed anchor point in the past, known as a "base year." It strips away inflation, showing whether a country actually produced more physical goods and services. 
+&gt; When you read headlines saying "a country's economy grew by 7%," they are talking about Real GDP.
+### Factors of production
+The four elements (Land, Labor, Capital, Entrepreneurship) are called the factors of production. 
+&gt; Money is called "financial capital". Capital is something different
+- `Land` : Includes all natural resources used in production, such as soil, water, forests, minerals, and geographical resources. Land is a fixed or limited factor in many situations, so its productivity depends on irrigation, technology, conservation, and efficient use
+- `Labour` (Human Effort) : Physical and mental effort people contribute to production. Quality of labour depends on education, skills, health, training, and work conditions. 
+- `Capital` : Includes human-made assets used to produce other goods and services, such as machinery, factories, computers, warehouses, and infrastructure. Investment in physical capital can raise output per worker, although it requires financing, maintenance, and suitable technology
+- `Entrepreneurship (Organisation and Risk-Taking)` : Ability to combine the other factors of production, make business decisions, identify opportunities, and bear business risks. They help introduce innovations, create jobs, and move resources towards products consumers want
+### Combining 4 factors of production
+Economy (GDP) is defined on the following factors : $Y$ represents total output or real GDP, $L$ represents labour, $K$ represents physical capital, $N$ represents land and natural resources, $E$ represents entrepreneurial ability, and $A$ represents technology and overall efficiency
+$$
+\begin{aligned}
+Y = A \times F(L,K,N,E)
+\end{aligned}
+$$
+The impact of these factors are : More productive labour and better capital can increase real GDP, while new enterprises can create employment and introduce more efficient production methods. Efficient land use can improve agricultural productivity and reduce resource shortages, while shortages of skills, infrastructure, or energy can raise production costs and contribute to inflationary pressure.
+&gt; More of a conceptual model. A region may have abundant mineral resources but limited local industrial development if it lacks reliable infrastructure, skilled workers, investment, or effective business organisation. Similarly, a large workforce will not automatically create high GDP growth if many people remain unemployed, underemployed, or engaged in low-productivity work.
+### Indian economy in context
+Agriculture still supports a substantial share of the workforce, so better irrigation, storage, technology, and access to markets can raise rural productivity. Manufacturing and infrastructure investment can increase demand for labour and capital, while education, vocational training, and digital skills can help workers move into higher-productivity activities.
+Entrepreneurship is particularly important because it connects resources to market demand, but entrepreneurs also need reliable electricity, transport, finance, predictable regulations, and access to skilled workers</t>
   </si>
 </sst>
 </file>
@@ -415,7 +454,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F3">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="3"/>
@@ -719,13 +758,25 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+    <row r="3" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -29509,7 +29560,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{5817FDCF-08EC-44F6-84BD-8A54B3224FD6}"/>
+      <autoFilter ref="A1:F23" xr:uid="{1B91CF62-B7F9-47AF-9972-F8F1836D48E2}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD07C06C-80A5-4F0C-93CE-14539FACF9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8ED01E-8443-46A2-AD79-F65CBB51A1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="-15810" windowWidth="29040" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$3</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Domain</t>
   </si>
@@ -175,6 +175,57 @@
 ### Indian economy in context
 Agriculture still supports a substantial share of the workforce, so better irrigation, storage, technology, and access to markets can raise rural productivity. Manufacturing and infrastructure investment can increase demand for labour and capital, while education, vocational training, and digital skills can help workers move into higher-productivity activities.
 Entrepreneurship is particularly important because it connects resources to market demand, but entrepreneurs also need reliable electricity, transport, finance, predictable regulations, and access to skilled workers</t>
+  </si>
+  <si>
+    <t>Maketing</t>
+  </si>
+  <si>
+    <t>Brand equity and value</t>
+  </si>
+  <si>
+    <t>Generic</t>
+  </si>
+  <si>
+    <t>A brand is a psychological promise, Brand Equity is how deeply your audience believes that promise, and Brand Value is the financial reward you get for keeping it. Consumers face intense decision fatigue every day. If someone is buying a new smartphone, they don't have the time or energy to read the specs, compare different modes, or benchmark the processors. Instead, their brain uses a shortcut: _Apple means premium and easy to use. Samsung means cutting-edge tech._</t>
+  </si>
+  <si>
+    <t>To clear up a common trap right away: **Brand value _is_ a monetary value.** It is the literal financial amount your brand would sell for if you put it on the open market. Brand equity is the perceived worth of the brand in the customer's mind.
+A generic company needs to fight for every single sale using discounts, performance specs, and expensive ad campaigns. But if a company has high brand value, marketing becomes infinitely cheaper and more effective. Brand equity allows you to:
+- **Charge a premium:** People pay $150 for a Nike shoe that costs $15 to make.
+- **Launch new products easily:** When Sony launches a new PlayStation, millions pre-order it before seeing a single frame of gameplay, purely on trust.
+- **Survive mistakes:** If a trusted brand ships a buggy update, users wait for a patch. If an unknown brand does it, users immediately refund and leave a negative review.
+### Building the brand equity
+- Ensure the actual product delivers exactly what your ads promise. A massive marketing budget cannot fix a broken product. If you don't deliver on your promise, brand equity plummets.
+- Ensure the _perception_ of quality matches or exceeds the actual quality. It doesn't matter if your software is objectively 10% faster than the competitor if the user interface looks clunky
+- Focus on creating retention. It is vastly more profitable to keep a high fan following than to constantly pay for new user acquisition
+```mermaid
+mindmap
+  root((BUILDING BRAND VALUE))
+    DELIVER ON THE PROMISE
+      Ensure actual product delivers exactly what ads promise
+      A massive marketing budget cannot fix a broken product
+      If you don't deliver on your promise, brand equity plummets
+    MANAGE PERCEPTION OF QUALITY
+      Ensure perception of quality matches or exceeds actual quality
+      A clunky UI ruins fast software
+      How it feels matters as much as how it works
+    DRIVE RETENTION OVER ACQUISITION
+      Focus on creating retention
+      Vastly more profitable to keep a high fan following
+      Lower costs compared to constantly paying for new user acquisition
+```
+### Quantifying value of a brand
+The brand value refers to the amount at which the brand could be sold in open market. There are few methods to calculate it
+- `Cost-Based Approach`: Calculating how much it would cost to build that exact brand from scratch today. You add up all historical marketing, design, advertising, and R&amp;D expenses that went into creating the brand's current status.   
+- `Market-Based Approach`: Looking at what similar brands in your industry recently sold for. It is exactly like looking at "comps" when selling a house—if a rival software company with similar market share sold its trademark for $50 million, yours is likely in that ballpark.   
+- `Income-Based Approach`: Calculating the extra future cash flow the brand generates. If a generic mechanical keyboard sells for $40 and a Razer keyboard with the exact same specs sells for $120, the brand is generating $80 of premium income per unit. You forecast that extra income over several years and discount it to present value.   
+### Explaining the income based approach
+If a generic mechanical keyboard sells for $40 and a Razer keyboard with the exact same specs sells for $120
+- **The Premium:** The hardware is $40, but the logo adds an $80 psychological tax per sale.
+- **The Yearly Run-Rate:** Selling 1 million keyboards means the brand alone prints an extra $80 million annually.
+- **The Future Total:** Over 5 years, that is $400 million in bonus cash a generic competitor misses out on.
+- **Time Value of Money:** Future money is worth less than today's money because you cannot invest it right now, and consumer hype is always a risk.
+- **The Discount:** Accountants mathematically shrink that risky future $400 million into today's money, officially valuing the brand at a lump sum of $320 million right now.</t>
   </si>
 </sst>
 </file>
@@ -454,7 +505,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F4">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="3"/>
@@ -799,13 +850,25 @@
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
     </row>
-    <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+    <row r="4" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -29560,7 +29623,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{1B91CF62-B7F9-47AF-9972-F8F1836D48E2}"/>
+      <autoFilter ref="A1:F23" xr:uid="{11E4EC6A-87F4-44BC-9779-5E25E2096EDE}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8ED01E-8443-46A2-AD79-F65CBB51A1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C17F529-059F-48FA-A305-913C3526A171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4065" yWindow="-15810" windowWidth="29040" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$4</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Domain</t>
   </si>
@@ -59,173 +59,25 @@
     <t>Pick Count</t>
   </si>
   <si>
-    <t>Math and Statistics</t>
+    <t>Sustainability</t>
   </si>
   <si>
-    <t>Cluster vs Stratified sampling</t>
+    <t>Emissions (Scope X)</t>
   </si>
   <si>
-    <t>Statistics</t>
+    <t>Scope 2 location vs market based reporting</t>
   </si>
   <si>
-    <t>Sampling is the process of selecting a subset of a population to draw conclusions about the whole. It saves time, cost, and effort while making research practical. The key methods include stratified sampling, which takes samples from every group; cluster sampling, which studies selected groups; and multi-stage sampling, which selects samples in multiple steps, from larger groups to smaller units.</t>
+    <t>A factory needs power. They get this from local energy grid. This grid gets powers from various electricity generation centers. The way it reports its emissions differs based on commitment to renewable energy</t>
   </si>
   <si>
-    <t>Cluster sampling and stratified sampling differ mainly in what you select and why you select it. In stratified sampling, you divide the population into groups and sample from every group, while in cluster sampling, you divide the population into groups and select only some groups for study.
-Imagine XLRI has 1,000 students across different programs and years. You want to survey students about campus life, so you need a way to select a manageable sample.
-### Stratified sampling
-Take some students from every group. Divide the students into **strata**, such as `BM (Business Management)`, `HRM (Human Resource Management)`, and other programs, then randomly select students from each group. This ensures every program is represented in your sample.
-```mermaid
-flowchart TD
-    A["All MBA Students"] --&gt; B["BM"]
-    A --&gt; C["HRM"]
-    A --&gt; D["Other Programs"]
-    B --&gt; E["Randomly Select Students"]
-    C --&gt; F["Randomly Select Students"]
-    D --&gt; G["Randomly Select Students"]
-    E --&gt; H["Final Sample"]
-    F --&gt; H
-    G --&gt; H
-    classDef group fill:#DCEBFA,stroke:#3973AC,color:#163A5C
-    classDef result fill:#DDF3E4,stroke:#39845A,color:#174D2D
-    class B,C,D,E,F,G group
-    class H result
-```
-### Cluster sampling
-Divide the students into clusters, such as year (first year or second year), sections etc. You survey students in those selected sections rather than sampling from every section. Ideally, each cluster reflects the wider population. 
-```mermaid
-flowchart TD
-    A["All MBA Students"] --&gt; B["Section 1"]
-    A --&gt; C["Section 2"]
-    A --&gt; D["Section 3"]
-    A --&gt; E["Section 4"]
-    B --&gt; F["Selected"]
-    D --&gt; F
-    F --&gt; G["Survey All Students in Selected Sections"]
-    G --&gt; H["Final Sample"]
-    classDef group fill:#DCEBFA,stroke:#3973AC,color:#163A5C
-    classDef selected fill:#FBE7C6,stroke:#B7791F,color:#704214
-    classDef result fill:#DDF3E4,stroke:#39845A,color:#174D2D
-    class B,C,D,E group
-    class F,G selected
-    class H result
-```
-### Summary of these methods
-| Basis          | Stratified sampling                         | Cluster sampling                                    |
-| -------------- | ------------------------------------------- | --------------------------------------------------- |
-| Selection      | Some members from every stratum             | Some clusters from the population                   |
-| Groups         | Similar members within each stratum         | Ideally, each cluster reflects the wider population |
-| Main objective | Ensure representation and improve precision | Reduce cost and effort                              |
-| Example        | Students sampled from every program         | A few tutorial sections selected                    |
-&gt; [!tip]
-&gt; Stratified means all groups represented; cluster means some groups selected
-### Cluster Sampling Iteratively
-After creating clusters, we can further create clusters to pinpoint the criteria of people we need. Imagine you want to survey MBA students across India, but you cannot visit every college, so you randomly select 3 states, then 4 colleges in each state, then 2 classes in each college, and finally 10 students from each class. You have selected your sample through four stages, giving you \(3 \times 4 \times 2 \times 10 = 240\) students.
-```mermaid
-flowchart TD
-    A["MBA Students Across India"]
-    A --&gt; B["Stage 1: Select 3 States"]
-    B --&gt; C["Stage 2: Select 4 Colleges per State"]
-    C --&gt; D["Stage 3: Select 2 Classes per College"]
-    D --&gt; E["Stage 4: Select 10 Students per Class"]
-    E --&gt; F["Final Sample: 240 Students"]
-    style A fill:#E5E7EB,stroke:#6B7280,color:#111827
-    style B fill:#DBEAFE,stroke:#2563EB,color:#1E3A8A
-    style C fill:#D1FAE5,stroke:#059669,color:#064E3B
-    style D fill:#FEF3C7,stroke:#D97706,color:#78350F
-    style E fill:#F3E8FF,stroke:#9333EA,color:#581C87
-    style F fill:#DCFCE7,stroke:#16A34A,color:#14532D
-```</t>
-  </si>
-  <si>
-    <t>Economics</t>
-  </si>
-  <si>
-    <t>Factors of production</t>
-  </si>
-  <si>
-    <t>Macroeconomics</t>
-  </si>
-  <si>
-    <t>An economy can be understood as a system in which Land, Labour, Capital, and Entrepreneurship work together to produce goods and services, generate income, and improve people's standard of living. Land provides the natural resources, labour provides the workers doing the work, capital provides the tools and equipment, and entrepreneurship acts like the strategist who brings everything together. When these factors combine efficiently, the economy can produce more output, create jobs, and grow its GDP.</t>
-  </si>
-  <si>
-    <t>### GDP
-It is the total monetary value of all final goods and services produced within a country's borders in a specific time frame (usually a year). It is the ultimate scoreboard for a country, measuring its economic size, output, and overall health.
-Economists created different types of GDP to separate the illusion of rising prices from actual, tangible growth in production. If one thing that costed 100 previous year but now costs 110, it's not that the economy got bigger, just that the money lost its value $\implies$ you pay more for the same thing as before
-- **Nominal GDP**: This is GDP measured at current market prices. It includes the effects of inflation
-- **Real GDP**: Inflation-adjusted score. Calculates the value of goods using the prices from a fixed anchor point in the past, known as a "base year." It strips away inflation, showing whether a country actually produced more physical goods and services. 
-&gt; When you read headlines saying "a country's economy grew by 7%," they are talking about Real GDP.
-### Factors of production
-The four elements (Land, Labor, Capital, Entrepreneurship) are called the factors of production. 
-&gt; Money is called "financial capital". Capital is something different
-- `Land` : Includes all natural resources used in production, such as soil, water, forests, minerals, and geographical resources. Land is a fixed or limited factor in many situations, so its productivity depends on irrigation, technology, conservation, and efficient use
-- `Labour` (Human Effort) : Physical and mental effort people contribute to production. Quality of labour depends on education, skills, health, training, and work conditions. 
-- `Capital` : Includes human-made assets used to produce other goods and services, such as machinery, factories, computers, warehouses, and infrastructure. Investment in physical capital can raise output per worker, although it requires financing, maintenance, and suitable technology
-- `Entrepreneurship (Organisation and Risk-Taking)` : Ability to combine the other factors of production, make business decisions, identify opportunities, and bear business risks. They help introduce innovations, create jobs, and move resources towards products consumers want
-### Combining 4 factors of production
-Economy (GDP) is defined on the following factors : $Y$ represents total output or real GDP, $L$ represents labour, $K$ represents physical capital, $N$ represents land and natural resources, $E$ represents entrepreneurial ability, and $A$ represents technology and overall efficiency
-$$
-\begin{aligned}
-Y = A \times F(L,K,N,E)
-\end{aligned}
-$$
-The impact of these factors are : More productive labour and better capital can increase real GDP, while new enterprises can create employment and introduce more efficient production methods. Efficient land use can improve agricultural productivity and reduce resource shortages, while shortages of skills, infrastructure, or energy can raise production costs and contribute to inflationary pressure.
-&gt; More of a conceptual model. A region may have abundant mineral resources but limited local industrial development if it lacks reliable infrastructure, skilled workers, investment, or effective business organisation. Similarly, a large workforce will not automatically create high GDP growth if many people remain unemployed, underemployed, or engaged in low-productivity work.
-### Indian economy in context
-Agriculture still supports a substantial share of the workforce, so better irrigation, storage, technology, and access to markets can raise rural productivity. Manufacturing and infrastructure investment can increase demand for labour and capital, while education, vocational training, and digital skills can help workers move into higher-productivity activities.
-Entrepreneurship is particularly important because it connects resources to market demand, but entrepreneurs also need reliable electricity, transport, finance, predictable regulations, and access to skilled workers</t>
-  </si>
-  <si>
-    <t>Maketing</t>
-  </si>
-  <si>
-    <t>Brand equity and value</t>
-  </si>
-  <si>
-    <t>Generic</t>
-  </si>
-  <si>
-    <t>A brand is a psychological promise, Brand Equity is how deeply your audience believes that promise, and Brand Value is the financial reward you get for keeping it. Consumers face intense decision fatigue every day. If someone is buying a new smartphone, they don't have the time or energy to read the specs, compare different modes, or benchmark the processors. Instead, their brain uses a shortcut: _Apple means premium and easy to use. Samsung means cutting-edge tech._</t>
-  </si>
-  <si>
-    <t>To clear up a common trap right away: **Brand value _is_ a monetary value.** It is the literal financial amount your brand would sell for if you put it on the open market. Brand equity is the perceived worth of the brand in the customer's mind.
-A generic company needs to fight for every single sale using discounts, performance specs, and expensive ad campaigns. But if a company has high brand value, marketing becomes infinitely cheaper and more effective. Brand equity allows you to:
-- **Charge a premium:** People pay $150 for a Nike shoe that costs $15 to make.
-- **Launch new products easily:** When Sony launches a new PlayStation, millions pre-order it before seeing a single frame of gameplay, purely on trust.
-- **Survive mistakes:** If a trusted brand ships a buggy update, users wait for a patch. If an unknown brand does it, users immediately refund and leave a negative review.
-### Building the brand equity
-- Ensure the actual product delivers exactly what your ads promise. A massive marketing budget cannot fix a broken product. If you don't deliver on your promise, brand equity plummets.
-- Ensure the _perception_ of quality matches or exceeds the actual quality. It doesn't matter if your software is objectively 10% faster than the competitor if the user interface looks clunky
-- Focus on creating retention. It is vastly more profitable to keep a high fan following than to constantly pay for new user acquisition
-```mermaid
-mindmap
-  root((BUILDING BRAND VALUE))
-    DELIVER ON THE PROMISE
-      Ensure actual product delivers exactly what ads promise
-      A massive marketing budget cannot fix a broken product
-      If you don't deliver on your promise, brand equity plummets
-    MANAGE PERCEPTION OF QUALITY
-      Ensure perception of quality matches or exceeds actual quality
-      A clunky UI ruins fast software
-      How it feels matters as much as how it works
-    DRIVE RETENTION OVER ACQUISITION
-      Focus on creating retention
-      Vastly more profitable to keep a high fan following
-      Lower costs compared to constantly paying for new user acquisition
-```
-### Quantifying value of a brand
-The brand value refers to the amount at which the brand could be sold in open market. There are few methods to calculate it
-- `Cost-Based Approach`: Calculating how much it would cost to build that exact brand from scratch today. You add up all historical marketing, design, advertising, and R&amp;D expenses that went into creating the brand's current status.   
-- `Market-Based Approach`: Looking at what similar brands in your industry recently sold for. It is exactly like looking at "comps" when selling a house—if a rival software company with similar market share sold its trademark for $50 million, yours is likely in that ballpark.   
-- `Income-Based Approach`: Calculating the extra future cash flow the brand generates. If a generic mechanical keyboard sells for $40 and a Razer keyboard with the exact same specs sells for $120, the brand is generating $80 of premium income per unit. You forecast that extra income over several years and discount it to present value.   
-### Explaining the income based approach
-If a generic mechanical keyboard sells for $40 and a Razer keyboard with the exact same specs sells for $120
-- **The Premium:** The hardware is $40, but the logo adds an $80 psychological tax per sale.
-- **The Yearly Run-Rate:** Selling 1 million keyboards means the brand alone prints an extra $80 million annually.
-- **The Future Total:** Over 5 years, that is $400 million in bonus cash a generic competitor misses out on.
-- **Time Value of Money:** Future money is worth less than today's money because you cannot invest it right now, and consumer hype is always a risk.
-- **The Discount:** Accountants mathematically shrink that risky future $400 million into today's money, officially valuing the brand at a lump sum of $320 million right now.</t>
+    <t>A factory needs power. They get this from local energy grid. This grid gets powers from various electricity generation centers. For this example, let's say
+1. A thermal power plant that uses coal (70%)
+2. A solar farm (30%)
+Let us assume that using both the energy resources, emission is 0.5 per MWh and without solar, emission is 0.6 per MWh
+- Location based : Use the full mix. 0.5 per MWh
+- Market based : Take renewable as 0 and take remaining as 0.6
+Location-based accounting asks, “What is the average emissions intensity of the grid supplying this facility?” Market-based accounting asks, “What emissions attributes (renewable and non renewable) are associated with the electricity the company has contractually chosen?” They should not be mixed up or treated as interchangeable.</t>
   </si>
 </sst>
 </file>
@@ -505,7 +357,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="3"/>
@@ -722,7 +574,7 @@
   <dimension ref="A1:AA1000"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.3984375" customWidth="1"/>
+    <col min="1" max="1" width="11.46484375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.59765625" customWidth="1"/>
     <col min="3" max="3" width="11.53125" customWidth="1"/>
     <col min="4" max="4" width="27.46484375" customWidth="1"/>
@@ -770,15 +622,15 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="178.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
@@ -809,25 +661,13 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
+    <row r="3" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -850,25 +690,13 @@
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
     </row>
-    <row r="4" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
+    <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -28964,12 +28792,6 @@
       <c r="AA972" s="1"/>
     </row>
     <row r="973" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A973" s="1"/>
-      <c r="B973" s="1"/>
-      <c r="C973" s="1"/>
-      <c r="D973" s="1"/>
-      <c r="E973" s="1"/>
-      <c r="F973" s="1"/>
       <c r="G973" s="1"/>
       <c r="H973" s="1"/>
       <c r="I973" s="1"/>
@@ -28993,12 +28815,6 @@
       <c r="AA973" s="1"/>
     </row>
     <row r="974" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A974" s="1"/>
-      <c r="B974" s="1"/>
-      <c r="C974" s="1"/>
-      <c r="D974" s="1"/>
-      <c r="E974" s="1"/>
-      <c r="F974" s="1"/>
       <c r="G974" s="1"/>
       <c r="H974" s="1"/>
       <c r="I974" s="1"/>
@@ -29623,7 +29439,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{11E4EC6A-87F4-44BC-9779-5E25E2096EDE}"/>
+      <autoFilter ref="A1:F23" xr:uid="{AF1F287C-8B6B-4F2C-98FF-06FFD5F35E6F}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C17F529-059F-48FA-A305-913C3526A171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA9363A-560A-48BA-AE05-D7EE59C9EF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,12 @@
     <t>A factory needs power. They get this from local energy grid. This grid gets powers from various electricity generation centers. The way it reports its emissions differs based on commitment to renewable energy</t>
   </si>
   <si>
-    <t>A factory needs power. They get this from local energy grid. This grid gets powers from various electricity generation centers. For this example, let's say
+    <t>There are various categories of emissions
+- Scope 1 (Direct emissions) : emissions from sources the company owns or controls. Examples include burning coal or natural gas in a factory boiler, using fuel in company-owned vehicles, and releasing gases during industrial processes
+2. Scope 2 (Purchased energy emissions) : associated with generating the electricity, steam, heating, or cooling a company purchases and consumes. The emissions occur at the power station, not necessarily at the company's premises, but the company accounts for them because it uses that energy
+3. Scope 3 (Other indirect emissions) : emissions from activities across the company's value chain that are not already counted in Scope 1 or Scope 2. 
+### Scope 2 emissions and need of power from external sources
+A factory needs power. They get this from local energy grid. This grid gets powers from various electricity generation centers. For this example, let's say
 1. A thermal power plant that uses coal (70%)
 2. A solar farm (30%)
 Let us assume that using both the energy resources, emission is 0.5 per MWh and without solar, emission is 0.6 per MWh
@@ -622,7 +627,7 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="178.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="369.75" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35309B41-DEA0-4ABC-9E02-B68B62EA5AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BC8A7D-C2C9-4790-86CC-09370C1B30E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$3</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Domain</t>
   </si>
@@ -62,49 +62,38 @@
     <t>Working with yourself</t>
   </si>
   <si>
-    <t>Meeting people through shared activities</t>
+    <t>Life stages and meaning</t>
   </si>
   <si>
-    <t>Socializing</t>
+    <t>Purpose</t>
   </si>
   <si>
-    <t>Meeting people through shared activities requires a recurring, low-stakes, structured social channel that fits one's personality</t>
+    <t>Meaningful life isn’t one fixed thing. What matters most shifts with each decade, like a game that changes its rules at each level. In your 20s you **explore**, in your 30s you **commit**, in your 40s you **cut**, in your 50s you **teach**, in your 60s you **rediscover**, in your 70s you **connect**, and in your 80s you **pass things on**. Each stage has a theme and one small action.</t>
   </si>
   <si>
-    <t>A billiards league/regular table, a drawing class, a board-games meetup, a reading group. All of these interests can become activities through which one can meet people. The overwhelm with socializing in general ("too many steps to process") is real, and one of the fixes is to reduce it to _one_ step: pick one channel, commit to showing up twice, then decide. Not "figure out how to meet people" but "Show up at X on Tuesday".</t>
+    <t xml:space="preserve">
+| Decade  | Theme      | Core Idea                                                                                                                                                                  | Action                                                                               |
+| ------- | ---------- | -------------------------------------------------------------------------------------------------------------------------------------------------------------------------- | ------------------------------------------------------------------------------------ |
+| **20s** | Experience | Collect experiences before you collect obligations. Try jobs, places, relationships and interests to learn what kind of life you actually enjoy living.                    | Try something you've been curious about without asking whether it helps your career. |
+| **30s** | Commit     | Meaning starts requiring choices. Time is limited across work, relationships, family, friends and yourself, so decide what gets genuine commitment.                        | Choose one relationship or priority that deserves more of your time this month.      |
+| **40s** | Edit       | Success can leave you carrying goals you no longer care about. Some ambitions deserve another decade; others have been on the list too long.                               | Remove one goal you're pursuing mostly because of expectation, status or habit.      |
+| **50s** | Share      | What you've learned becomes useful to someone behind you. Your mistakes, judgement and experience can save others years of figuring things out alone.                      | Give one younger person an hour of your time with no agenda attached.                |
+| **60s** | Redefine   | Work may stop being the main answer to "what do you do?" That creates space to rediscover interests, relationships and parts of yourself your career couldn't accommodate. | Restart something you enjoyed before work became the centre of your week.            |
+| **70s** | Belong     | The people around you matter enormously. Friendships and communities don't maintain themselves once work stops filling your calendar with people.                          | Create one recurring reason to see people you enjoy being around.                    |
+| **80s** | Give       | Your attention, stories, experience and presence still matter to the people around you. Milestones should take a back seat.                                                | Pass something on: a lesson, tradition, skill or story worth keeping.                |</t>
   </si>
   <si>
-    <t>Working with others</t>
+    <t>Link</t>
   </si>
   <si>
-    <t>Leaning and outsourcing</t>
-  </si>
-  <si>
-    <t>Relationships</t>
-  </si>
-  <si>
-    <t>Leaning means that you keep the ownership of what needs to be done. Outsourcing is being entirely dependent on them and having no ownership. In the leaning case, you will somehow find a way of getting things done. In outsourcing, you don't even think of doing it on your own and just panic or find someone else who will take the ownership</t>
-  </si>
-  <si>
-    <t>### I want a relationship where she compensates the part that is missing in me" be careful with the frame : Difference between leaning and outsourcing
-In relationships, reciprocal value is necessary. If partner is not available for a while (or for a long while), would things still get done albeit inefficiently? If yes, then it is leaning else outsourcing
-Leaning tends to make you slightly less dependent over time ; not because you're trying to replace her, but because proximity transfers competence. You pick things up. You get better at the edges. After five years of leaning on her for X, you can do 30% of X yourself and you understand the other 70% well enough to know when it's going wrong. Outsourcing makes you more dependent over time ; or at best flat. After five years, you can do 0% of X and you don't even know when it's going wrong. You've not just delegated the task; you've delegated the ability to evaluate the task. That's the real cost.
-Ultimately, leaning should result in
-- Being able to handle the situation when the support is removed. If she were unavailable for 6 months, would the work still get done?
-- Am I able to determine what or when something needs to be done? Have I learnt anything in the process? 
-### Failure mode 2: The quiet resentment of the "competent" partner
-The other version: you find someone genuinely strong : high-C, high-E, capable. She compensates beautifully. And then, over years, you notice something: **you resent her for being the one who does the things you can't.** Not consciously, not fairly : but the resentment is structural. Every time she organizes the trip, handles the social logistics, manages the emotional weather, you're reminded of the deficit. The relationship becomes a standing indictment of the part of you you've outsourced. And avoidant people don't process resentment by talking about it; they process it by **withdrawing**. So the relationship slowly hollows out from the inside while looking functional from the outside.
-This is why "she compensates what's missing in me" is a _stable-looking but corrosive_ frame. It produces a relationship that works : until the ledger of unspoken deficits gets too heavy.
-### Result
-The centipede model (building a strong spine and small extensions on it) is your answer to the deadline version. **The reciprocal relationship frame is your answer to the partner version.** Both say the same thing: _I will build the spine myself, cheaply and incrementally, and then I will choose people to lean on and cover : not people to be the spine._
-**For each one, run the six-month test.** Sort into "leanable" (fine to want help) vs. "collapse" (goes on the centipede list as a spine task).</t>
+    <t>https://beardedowl1357.github.io/Personal_Blog/working-with-yourself/life-stages-and-meaning/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -123,6 +112,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -146,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -164,17 +159,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <b val="0"/>
@@ -195,6 +187,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -231,6 +226,27 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -355,22 +371,22 @@
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="Knowledge-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="secondRowStripe" dxfId="14"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="secondRowStripe" dxfId="15"/>
     </tableStyle>
     <tableStyle name="Compounding Reminder-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="13"/>
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="secondRowStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="secondRowStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="Master Quotes-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="10"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -385,14 +401,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:F3" dataDxfId="3">
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:G2" dataDxfId="6">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Category" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Definition/Formula" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Explanation" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Definition/Formula" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Explanation" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Pick Count" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{86FA0ABF-0969-4887-8E77-67BFEE7C42E2}" name="Link" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Knowledge-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -599,7 +616,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA1000"/>
+  <dimension ref="A1:AA999"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.46484375" style="6" bestFit="1" customWidth="1"/>
@@ -629,7 +646,9 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -651,7 +670,7 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="63.75" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="242.25" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -670,7 +689,9 @@
       <c r="F2" s="5">
         <v>0</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -692,25 +713,13 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" ht="395.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
+    <row r="3" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -762,7 +771,7 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
-    <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1284,7 +1293,7 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -28806,12 +28815,6 @@
       <c r="AA971" s="1"/>
     </row>
     <row r="972" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A972" s="5"/>
-      <c r="B972" s="5"/>
-      <c r="C972" s="5"/>
-      <c r="D972" s="5"/>
-      <c r="E972" s="5"/>
-      <c r="F972" s="5"/>
       <c r="G972" s="1"/>
       <c r="H972" s="1"/>
       <c r="I972" s="1"/>
@@ -29455,34 +29458,11 @@
       <c r="Z999" s="1"/>
       <c r="AA999" s="1"/>
     </row>
-    <row r="1000" spans="7:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="G1000" s="1"/>
-      <c r="H1000" s="1"/>
-      <c r="I1000" s="1"/>
-      <c r="J1000" s="1"/>
-      <c r="K1000" s="1"/>
-      <c r="L1000" s="1"/>
-      <c r="M1000" s="1"/>
-      <c r="N1000" s="1"/>
-      <c r="O1000" s="1"/>
-      <c r="P1000" s="1"/>
-      <c r="Q1000" s="1"/>
-      <c r="R1000" s="1"/>
-      <c r="S1000" s="1"/>
-      <c r="T1000" s="1"/>
-      <c r="U1000" s="1"/>
-      <c r="V1000" s="1"/>
-      <c r="W1000" s="1"/>
-      <c r="X1000" s="1"/>
-      <c r="Y1000" s="1"/>
-      <c r="Z1000" s="1"/>
-      <c r="AA1000" s="1"/>
-    </row>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{FE27714C-26F1-4CE4-98E6-5A6880582F54}"/>
+      <autoFilter ref="A1:F23" xr:uid="{6ECF2C7A-0607-4921-AACF-1B08683485F2}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quotes.xlsx
+++ b/Quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding_Projects\Personal_Blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BC8A7D-C2C9-4790-86CC-09370C1B30E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA05DA40-92E8-46A6-A30B-59E447245FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="413" windowWidth="19396" windowHeight="10964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Knowledge" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$2</definedName>
+    <definedName name="Z_1F027E93_A59B_48CA_AE68_028248C2B726_.wvu.FilterData" localSheetId="0" hidden="1">Knowledge!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Domain</t>
   </si>
@@ -87,6 +87,87 @@
   </si>
   <si>
     <t>https://beardedowl1357.github.io/Personal_Blog/working-with-yourself/life-stages-and-meaning/</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Contribution and margin of safety</t>
+  </si>
+  <si>
+    <t>Cost accounting</t>
+  </si>
+  <si>
+    <t>### Formula cheatsheet
+- $\text{contribution} = \text{Selling Price - Variable cost}$
+- $bep_{\text{number of items}} = \frac{\text{Fixed cost}}{\text{Contribution per item}}$
+- c/s ratio = $\frac{\text{Contribution per item}}{\text{Selling price of item}}$
+- Breakeven revenue = $\frac{\text{Fixed cost}}{\text{c/s ratio}}$
+- Margin of safety = $MoS =$ Total sales - Breakeven sales 
+- Margin of safety ratio = $\frac{\text{Margin of safety}}{\text{Total sales}}$
+- Net Profit = Total contribution - Fixed costs
+- Net Profit margin = c/s raito * margin of safety
+### Contribution
+Business has 2 types of costs
+- Fixed cost : Does not scale with a product upto a threshold
+- Variable cost : Scales with a product linearly (mostly)
+If we sell one product, we definitely price it higher than what it took to make it. The price that it took to make the product is called the variable cost. The difference between at the price on which item is sold and the price at which it was made is called `Contribution`
+$$
+\begin{aligned}
+\text{contribution} &amp;= \text{Selling Price - Variable cost} \\
+c &amp;= s - v_c
+\end{aligned}
+$$
+This "contribution" serves a purpose
+- Till a certain point, it justifies the cost (fixed) spent to make and sell the product
+- After a certain point, it directly leads to cash / profit
+- This certain point is called `Breakeven point` (BEP)
+### Breakeven point
+At breakeven point, `Total fixed cost = Contribution per item * n` , `n = `number of items sold
+$$
+\begin{aligned}
+bep_{\text{number of items}} &amp;= \frac{\text{Fixed cost}}{\text{Contribution per item}}
+\end{aligned}
+$$
+We can define a relationship that specifies that for each item sold, what portion of revenue is used to pay company's investment bills. This relationship or this ratio is called `c/s` ratio
+$$
+\begin{aligned}
+c_s &amp;= \frac{\text{Contribution per item}}{\text{Selling price of item}}
+\end{aligned}
+$$
+In terms of money, that is, the amount of sales that justify the fixed costs can be calculated as well. This is done through $c_s$ ratio
+$$
+\begin{aligned}
+bep_{\text{money}} &amp;= \frac{\text{Fixed cost}}{\text{c/s ratio}}
+\end{aligned}
+$$
+### Margin of safety
+&gt;[!note]
+&gt;Whenever we say `margin` in accounting, it means that we are comparing something with reference to its selling price $\implies \frac{\text{something}}{\text{selling price}}$
+After our sales reach the breakeven sales, we can say that the contribution earnt is now acting as the profit of the company that is, the amount of money that can be reinvested into business or withdrawn. Mathematically
+&gt; Margin of safety = $MoS =$ Total sakes - Breakeven sales 
+The ratio is calculated as 
+$$
+\begin{aligned}
+mos_{\text{ratio}} &amp;= \frac{\text{Margin of safety}}{\text{Total sales}}
+\end{aligned}
+$$
+&gt;[!tip]
+&gt;Essentially, it is just "% of sales that are pure profit"
+### Net Profit Margin
+Net profit is defined as `Total contribution - Fixed costs`. We can twist the formula to express the profit margin in terms of c/s ratio and margin of safety. The result is as follows
+```
+Net Profit margin = c/s raito * margin of safety
+```
+&gt;[!note]
+&gt;Profit margin = $\frac{\text{Net profit}}{\text{selling pice}}$
+### Why even care about this?
+- If the Break-Even Point is the line between life and death for a business, the Margin of Safety tells you how many steps you can safely take away from that cliff.
+- A high Margin of Safety (e.g., 50%) means you can survive market shocks—like a recession, a new competitor, or a supply chain failure. You have room to breathe and pivot.
+- Low MoS results in every single lost customer being a danger. This triggers immediate cost-cutting (lowering Fixed Costs) or desperate marketing (trying to boost Sales).</t>
+  </si>
+  <si>
+    <t>An overview of unit economics of a product going from loss-making to profit-making and how managers can observe and react</t>
   </si>
 </sst>
 </file>
@@ -401,7 +482,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:G2" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:G3" dataDxfId="6">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Topic" dataDxfId="5"/>
@@ -713,14 +794,26 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="1"/>
+    <row r="3" spans="1:27" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -29462,7 +29555,7 @@
   <customSheetViews>
     <customSheetView guid="{1F027E93-A59B-48CA-AE68-028248C2B726}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:F23" xr:uid="{6ECF2C7A-0607-4921-AACF-1B08683485F2}"/>
+      <autoFilter ref="A1:F23" xr:uid="{C8ABD902-102F-4927-8CB8-20221E3A63A4}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
